--- a/research/traditional_assets/database/data/poland/poland_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_transportation_railroads.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wse_pkp" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.009050000000000001</v>
+        <v>0.0133</v>
       </c>
       <c r="G2">
-        <v>0.1047761473034863</v>
+        <v>0.09296028880866426</v>
       </c>
       <c r="H2">
-        <v>0.1047761473034863</v>
+        <v>0.09296028880866426</v>
       </c>
       <c r="I2">
-        <v>-0.04495747266099635</v>
+        <v>0.004663056558363418</v>
       </c>
       <c r="J2">
-        <v>-0.04495747266099635</v>
+        <v>0.004663056558363418</v>
       </c>
       <c r="K2">
-        <v>-50.8</v>
+        <v>-15.5</v>
       </c>
       <c r="L2">
-        <v>-0.04748107299747639</v>
+        <v>-0.01554352186121139</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>32.8</v>
+        <v>25.7</v>
       </c>
       <c r="V2">
-        <v>0.2116129032258064</v>
+        <v>0.1732973701955496</v>
       </c>
       <c r="W2">
-        <v>-0.06200414988404736</v>
+        <v>-0.02018229166666667</v>
       </c>
       <c r="X2">
-        <v>0.1624643823248416</v>
+        <v>0.1900326955376664</v>
       </c>
       <c r="Y2">
-        <v>-0.224468532208889</v>
+        <v>-0.2102149872043331</v>
       </c>
       <c r="Z2">
-        <v>0.7599261311172668</v>
+        <v>0.7038893202512883</v>
       </c>
       <c r="AA2">
-        <v>-0.03416435826408126</v>
+        <v>0.003282275711159738</v>
       </c>
       <c r="AB2">
-        <v>0.05331929816932171</v>
+        <v>0.07888192106560524</v>
       </c>
       <c r="AC2">
-        <v>-0.08748365643340297</v>
+        <v>-0.07559964535444549</v>
       </c>
       <c r="AD2">
-        <v>681.5</v>
+        <v>512.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>681.5</v>
+        <v>512.2</v>
       </c>
       <c r="AG2">
-        <v>648.7</v>
+        <v>486.5000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.8147041243275552</v>
+        <v>0.7754731264193794</v>
       </c>
       <c r="AI2">
-        <v>0.4701621248706451</v>
+        <v>0.4506026216239993</v>
       </c>
       <c r="AJ2">
-        <v>0.8071419683961677</v>
+        <v>0.7663831127914303</v>
       </c>
       <c r="AK2">
-        <v>0.4578951083503918</v>
+        <v>0.437893789378938</v>
       </c>
       <c r="AL2">
-        <v>12.3</v>
+        <v>21.8</v>
       </c>
       <c r="AM2">
-        <v>11.494</v>
+        <v>20.951</v>
       </c>
       <c r="AN2">
-        <v>6.863041289023163</v>
+        <v>3.989096573208723</v>
       </c>
       <c r="AO2">
-        <v>-3.910569105691057</v>
+        <v>0.213302752293578</v>
       </c>
       <c r="AP2">
-        <v>6.532729103726084</v>
+        <v>3.788940809968848</v>
       </c>
       <c r="AQ2">
-        <v>-4.184792065425439</v>
+        <v>0.2219464464703356</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.009050000000000001</v>
+        <v>0.0133</v>
       </c>
       <c r="G3">
-        <v>0.1047761473034863</v>
+        <v>0.09296028880866426</v>
       </c>
       <c r="H3">
-        <v>0.1047761473034863</v>
+        <v>0.09296028880866426</v>
       </c>
       <c r="I3">
-        <v>-0.04495747266099635</v>
+        <v>0.004663056558363418</v>
       </c>
       <c r="J3">
-        <v>-0.04495747266099635</v>
+        <v>0.004663056558363418</v>
       </c>
       <c r="K3">
-        <v>-50.8</v>
+        <v>-15.5</v>
       </c>
       <c r="L3">
-        <v>-0.04748107299747639</v>
+        <v>-0.01554352186121139</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +760,8774 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>32.8</v>
+        <v>25.7</v>
       </c>
       <c r="V3">
-        <v>0.2116129032258064</v>
+        <v>0.1732973701955496</v>
       </c>
       <c r="W3">
-        <v>-0.06200414988404736</v>
+        <v>-0.02018229166666667</v>
       </c>
       <c r="X3">
-        <v>0.1624643823248416</v>
+        <v>0.1900326955376664</v>
       </c>
       <c r="Y3">
-        <v>-0.224468532208889</v>
+        <v>-0.2102149872043331</v>
       </c>
       <c r="Z3">
-        <v>0.7599261311172668</v>
+        <v>0.7038893202512883</v>
       </c>
       <c r="AA3">
-        <v>-0.03416435826408126</v>
+        <v>0.003282275711159738</v>
       </c>
       <c r="AB3">
-        <v>0.05331929816932171</v>
+        <v>0.07888192106560524</v>
       </c>
       <c r="AC3">
-        <v>-0.08748365643340297</v>
+        <v>-0.07559964535444549</v>
       </c>
       <c r="AD3">
-        <v>681.5</v>
+        <v>512.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>681.5</v>
+        <v>512.2</v>
       </c>
       <c r="AG3">
-        <v>648.7</v>
+        <v>486.5000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.8147041243275552</v>
+        <v>0.7754731264193794</v>
       </c>
       <c r="AI3">
-        <v>0.4701621248706451</v>
+        <v>0.4506026216239993</v>
       </c>
       <c r="AJ3">
-        <v>0.8071419683961677</v>
+        <v>0.7663831127914303</v>
       </c>
       <c r="AK3">
-        <v>0.4578951083503918</v>
+        <v>0.437893789378938</v>
       </c>
       <c r="AL3">
-        <v>12.3</v>
+        <v>21.8</v>
       </c>
       <c r="AM3">
-        <v>11.494</v>
+        <v>20.951</v>
       </c>
       <c r="AN3">
-        <v>6.863041289023163</v>
+        <v>3.989096573208723</v>
       </c>
       <c r="AO3">
-        <v>-3.910569105691057</v>
+        <v>0.213302752293578</v>
       </c>
       <c r="AP3">
-        <v>6.532729103726084</v>
+        <v>3.788940809968848</v>
       </c>
       <c r="AQ3">
-        <v>-4.184792065425439</v>
+        <v>0.2219464464703356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pkp Cargo S.A. (WSE:PKP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WSE:PKP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation (Railroads)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.775473126419379</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>148.3</v>
+      </c>
+      <c r="H2">
+        <v>550.303632056863</v>
+      </c>
+      <c r="I2">
+        <v>634.8</v>
+      </c>
+      <c r="J2">
+        <v>531.2086320568631</v>
+      </c>
+      <c r="K2">
+        <v>512.2</v>
+      </c>
+      <c r="L2">
+        <v>6.605</v>
+      </c>
+      <c r="M2">
+        <v>0.0788819210656052</v>
+      </c>
+      <c r="N2">
+        <v>0.0866983246072752</v>
+      </c>
+      <c r="O2">
+        <v>0.0466998440366973</v>
+      </c>
+      <c r="P2">
+        <v>0.759466161998486</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.190032695537666</v>
+      </c>
+      <c r="T2">
+        <v>0.0799026898861518</v>
+      </c>
+      <c r="U2">
+        <v>2.0506631103273</v>
+      </c>
+      <c r="V2">
+        <v>0.5573382765221</v>
+      </c>
+      <c r="W2">
+        <v>-11.4754950630011</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>148.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.05765412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>128.4</v>
+      </c>
+      <c r="AH2">
+        <v>146.5</v>
+      </c>
+      <c r="AI2">
+        <v>172.4</v>
+      </c>
+      <c r="AJ2">
+        <v>512.2</v>
+      </c>
+      <c r="AK2">
+        <v>512.2</v>
+      </c>
+      <c r="AL2">
+        <v>21.8</v>
+      </c>
+      <c r="AM2">
+        <v>512.2</v>
+      </c>
+      <c r="AN2">
+        <v>25.7</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-512.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>25.7</v>
+      </c>
+      <c r="H2">
+        <v>148.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>128.4</v>
+      </c>
+      <c r="K2">
+        <v>146.5</v>
+      </c>
+      <c r="L2">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="O2">
+        <v>-3.438999999999998</v>
+      </c>
+      <c r="P2">
+        <v>-14.661</v>
+      </c>
+      <c r="Q2">
+        <v>131.839</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08669832460727517</v>
+      </c>
+      <c r="C3">
+        <v>550.3036320568626</v>
+      </c>
+      <c r="D3">
+        <v>531.2086320568626</v>
+      </c>
+      <c r="E3">
+        <v>-505.595</v>
+      </c>
+      <c r="F3">
+        <v>6.605</v>
+      </c>
+      <c r="G3">
+        <v>25.7</v>
+      </c>
+      <c r="H3">
+        <v>148.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>128.4</v>
+      </c>
+      <c r="K3">
+        <v>146.5</v>
+      </c>
+      <c r="L3">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M3">
+        <v>1.577274</v>
+      </c>
+      <c r="N3">
+        <v>-19.67727399999999</v>
+      </c>
+      <c r="O3">
+        <v>-3.738682059999998</v>
+      </c>
+      <c r="P3">
+        <v>-15.93859193999999</v>
+      </c>
+      <c r="Q3">
+        <v>130.56140806</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07990268988615183</v>
+      </c>
+      <c r="T3">
+        <v>0.5573382765221003</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-2.180344061970208</v>
+      </c>
+      <c r="W3">
+        <v>0.7594661619984857</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-11.4754950630011</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08869832460727518</v>
+      </c>
+      <c r="C4">
+        <v>522.4069900533386</v>
+      </c>
+      <c r="D4">
+        <v>509.9169900533386</v>
+      </c>
+      <c r="E4">
+        <v>-498.9900000000001</v>
+      </c>
+      <c r="F4">
+        <v>13.21</v>
+      </c>
+      <c r="G4">
+        <v>25.7</v>
+      </c>
+      <c r="H4">
+        <v>148.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>128.4</v>
+      </c>
+      <c r="K4">
+        <v>146.5</v>
+      </c>
+      <c r="L4">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M4">
+        <v>3.154548000000001</v>
+      </c>
+      <c r="N4">
+        <v>-21.254548</v>
+      </c>
+      <c r="O4">
+        <v>-4.038364119999998</v>
+      </c>
+      <c r="P4">
+        <v>-17.21618388</v>
+      </c>
+      <c r="Q4">
+        <v>129.28381612</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08032210508907175</v>
+      </c>
+      <c r="T4">
+        <v>0.563025401792734</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-1.090172030985104</v>
+      </c>
+      <c r="W4">
+        <v>0.4991330809992429</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-5.737747531500548</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09069832460727517</v>
+      </c>
+      <c r="C5">
+        <v>496.1513753596283</v>
+      </c>
+      <c r="D5">
+        <v>490.2663753596283</v>
+      </c>
+      <c r="E5">
+        <v>-492.385</v>
+      </c>
+      <c r="F5">
+        <v>19.815</v>
+      </c>
+      <c r="G5">
+        <v>25.7</v>
+      </c>
+      <c r="H5">
+        <v>148.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>128.4</v>
+      </c>
+      <c r="K5">
+        <v>146.5</v>
+      </c>
+      <c r="L5">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M5">
+        <v>4.731821999999999</v>
+      </c>
+      <c r="N5">
+        <v>-22.831822</v>
+      </c>
+      <c r="O5">
+        <v>-4.338046179999998</v>
+      </c>
+      <c r="P5">
+        <v>-18.49377582</v>
+      </c>
+      <c r="Q5">
+        <v>128.00622418</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08075016802813434</v>
+      </c>
+      <c r="T5">
+        <v>0.5688297873782261</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-0.7267813539900694</v>
+      </c>
+      <c r="W5">
+        <v>0.4123553873328286</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-3.825165021000367</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09269832460727517</v>
+      </c>
+      <c r="C6">
+        <v>471.3541076432602</v>
+      </c>
+      <c r="D6">
+        <v>472.0741076432603</v>
+      </c>
+      <c r="E6">
+        <v>-485.78</v>
+      </c>
+      <c r="F6">
+        <v>26.42</v>
+      </c>
+      <c r="G6">
+        <v>25.7</v>
+      </c>
+      <c r="H6">
+        <v>148.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>128.4</v>
+      </c>
+      <c r="K6">
+        <v>146.5</v>
+      </c>
+      <c r="L6">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M6">
+        <v>6.309096000000001</v>
+      </c>
+      <c r="N6">
+        <v>-24.40909599999999</v>
+      </c>
+      <c r="O6">
+        <v>-4.637728239999998</v>
+      </c>
+      <c r="P6">
+        <v>-19.77136776</v>
+      </c>
+      <c r="Q6">
+        <v>126.72863224</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08118714894509407</v>
+      </c>
+      <c r="T6">
+        <v>0.574755097663416</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-0.545086015492552</v>
+      </c>
+      <c r="W6">
+        <v>0.3689665404996215</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-2.868873765750274</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09469832460727519</v>
+      </c>
+      <c r="C7">
+        <v>447.8586512311973</v>
+      </c>
+      <c r="D7">
+        <v>455.1836512311973</v>
+      </c>
+      <c r="E7">
+        <v>-479.1750000000001</v>
+      </c>
+      <c r="F7">
+        <v>33.025</v>
+      </c>
+      <c r="G7">
+        <v>25.7</v>
+      </c>
+      <c r="H7">
+        <v>148.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>128.4</v>
+      </c>
+      <c r="K7">
+        <v>146.5</v>
+      </c>
+      <c r="L7">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M7">
+        <v>7.88637</v>
+      </c>
+      <c r="N7">
+        <v>-25.98636999999999</v>
+      </c>
+      <c r="O7">
+        <v>-4.937410299999997</v>
+      </c>
+      <c r="P7">
+        <v>-21.0489597</v>
+      </c>
+      <c r="Q7">
+        <v>125.4510403</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.0816333294603056</v>
+      </c>
+      <c r="T7">
+        <v>0.5808051513230309</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-0.4360688123940416</v>
+      </c>
+      <c r="W7">
+        <v>0.3429332323996971</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-2.29509901260022</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09669832460727515</v>
+      </c>
+      <c r="C8">
+        <v>425.5300994939509</v>
+      </c>
+      <c r="D8">
+        <v>439.4600994939509</v>
+      </c>
+      <c r="E8">
+        <v>-472.5700000000001</v>
+      </c>
+      <c r="F8">
+        <v>39.63</v>
+      </c>
+      <c r="G8">
+        <v>25.7</v>
+      </c>
+      <c r="H8">
+        <v>148.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>128.4</v>
+      </c>
+      <c r="K8">
+        <v>146.5</v>
+      </c>
+      <c r="L8">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M8">
+        <v>9.463643999999999</v>
+      </c>
+      <c r="N8">
+        <v>-27.56364399999999</v>
+      </c>
+      <c r="O8">
+        <v>-5.237092359999997</v>
+      </c>
+      <c r="P8">
+        <v>-22.32655163999999</v>
+      </c>
+      <c r="Q8">
+        <v>124.17344836</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08208900317796841</v>
+      </c>
+      <c r="T8">
+        <v>0.5869839295285949</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-0.3633906769950347</v>
+      </c>
+      <c r="W8">
+        <v>0.3255776936664143</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-1.912582510500183</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09869832460727515</v>
+      </c>
+      <c r="C9">
+        <v>404.2515638858923</v>
+      </c>
+      <c r="D9">
+        <v>424.7865638858923</v>
+      </c>
+      <c r="E9">
+        <v>-465.965</v>
+      </c>
+      <c r="F9">
+        <v>46.23500000000001</v>
+      </c>
+      <c r="G9">
+        <v>25.7</v>
+      </c>
+      <c r="H9">
+        <v>148.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>128.4</v>
+      </c>
+      <c r="K9">
+        <v>146.5</v>
+      </c>
+      <c r="L9">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M9">
+        <v>11.040918</v>
+      </c>
+      <c r="N9">
+        <v>-29.140918</v>
+      </c>
+      <c r="O9">
+        <v>-5.536774419999998</v>
+      </c>
+      <c r="P9">
+        <v>-23.60414358</v>
+      </c>
+      <c r="Q9">
+        <v>122.89585642</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08255447633041968</v>
+      </c>
+      <c r="T9">
+        <v>0.5932955846848164</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-0.3114777231386011</v>
+      </c>
+      <c r="W9">
+        <v>0.313180880285498</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-1.639356437571585</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1006983246072752</v>
+      </c>
+      <c r="C10">
+        <v>383.9212630290103</v>
+      </c>
+      <c r="D10">
+        <v>411.0612630290104</v>
+      </c>
+      <c r="E10">
+        <v>-459.36</v>
+      </c>
+      <c r="F10">
+        <v>52.84</v>
+      </c>
+      <c r="G10">
+        <v>25.7</v>
+      </c>
+      <c r="H10">
+        <v>148.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>128.4</v>
+      </c>
+      <c r="K10">
+        <v>146.5</v>
+      </c>
+      <c r="L10">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M10">
+        <v>12.618192</v>
+      </c>
+      <c r="N10">
+        <v>-30.71819199999999</v>
+      </c>
+      <c r="O10">
+        <v>-5.836456479999997</v>
+      </c>
+      <c r="P10">
+        <v>-24.88173552</v>
+      </c>
+      <c r="Q10">
+        <v>121.61826448</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08303006846444599</v>
+      </c>
+      <c r="T10">
+        <v>0.5997444497357384</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-0.272543007746276</v>
+      </c>
+      <c r="W10">
+        <v>0.3038832702498107</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-1.434436882875137</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1026983246072752</v>
+      </c>
+      <c r="C11">
+        <v>364.4501584619367</v>
+      </c>
+      <c r="D11">
+        <v>398.1951584619367</v>
+      </c>
+      <c r="E11">
+        <v>-452.7550000000001</v>
+      </c>
+      <c r="F11">
+        <v>59.445</v>
+      </c>
+      <c r="G11">
+        <v>25.7</v>
+      </c>
+      <c r="H11">
+        <v>148.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>128.4</v>
+      </c>
+      <c r="K11">
+        <v>146.5</v>
+      </c>
+      <c r="L11">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M11">
+        <v>14.195466</v>
+      </c>
+      <c r="N11">
+        <v>-32.295466</v>
+      </c>
+      <c r="O11">
+        <v>-6.136138539999997</v>
+      </c>
+      <c r="P11">
+        <v>-26.15932746</v>
+      </c>
+      <c r="Q11">
+        <v>120.34067254</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08351611317284649</v>
+      </c>
+      <c r="T11">
+        <v>0.6063350480844827</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-0.2422604513300231</v>
+      </c>
+      <c r="W11">
+        <v>0.2966517957776095</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-1.275055007000122</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1046983246072752</v>
+      </c>
+      <c r="C12">
+        <v>345.7600209160278</v>
+      </c>
+      <c r="D12">
+        <v>386.1100209160278</v>
+      </c>
+      <c r="E12">
+        <v>-446.15</v>
+      </c>
+      <c r="F12">
+        <v>66.05</v>
+      </c>
+      <c r="G12">
+        <v>25.7</v>
+      </c>
+      <c r="H12">
+        <v>148.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>128.4</v>
+      </c>
+      <c r="K12">
+        <v>146.5</v>
+      </c>
+      <c r="L12">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M12">
+        <v>15.77274</v>
+      </c>
+      <c r="N12">
+        <v>-33.87273999999999</v>
+      </c>
+      <c r="O12">
+        <v>-6.435820599999997</v>
+      </c>
+      <c r="P12">
+        <v>-27.4369194</v>
+      </c>
+      <c r="Q12">
+        <v>119.0630806</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08401295887476701</v>
+      </c>
+      <c r="T12">
+        <v>0.6130721041743104</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-0.2180344061970208</v>
+      </c>
+      <c r="W12">
+        <v>0.2908666161998485</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-1.14754950630011</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1066983246072752</v>
+      </c>
+      <c r="C13">
+        <v>327.7818383478483</v>
+      </c>
+      <c r="D13">
+        <v>374.7368383478483</v>
+      </c>
+      <c r="E13">
+        <v>-439.5450000000001</v>
+      </c>
+      <c r="F13">
+        <v>72.655</v>
+      </c>
+      <c r="G13">
+        <v>25.7</v>
+      </c>
+      <c r="H13">
+        <v>148.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>128.4</v>
+      </c>
+      <c r="K13">
+        <v>146.5</v>
+      </c>
+      <c r="L13">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M13">
+        <v>17.350014</v>
+      </c>
+      <c r="N13">
+        <v>-35.450014</v>
+      </c>
+      <c r="O13">
+        <v>-6.735502659999997</v>
+      </c>
+      <c r="P13">
+        <v>-28.71451134</v>
+      </c>
+      <c r="Q13">
+        <v>117.78548866</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08452096964864081</v>
+      </c>
+      <c r="T13">
+        <v>0.6199605547830105</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.1982130965427462</v>
+      </c>
+      <c r="W13">
+        <v>0.2861332874544078</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-1.043226823909191</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1086983246072752</v>
+      </c>
+      <c r="C14">
+        <v>310.4544972773487</v>
+      </c>
+      <c r="D14">
+        <v>364.0144972773487</v>
+      </c>
+      <c r="E14">
+        <v>-432.9400000000001</v>
+      </c>
+      <c r="F14">
+        <v>79.25999999999999</v>
+      </c>
+      <c r="G14">
+        <v>25.7</v>
+      </c>
+      <c r="H14">
+        <v>148.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>128.4</v>
+      </c>
+      <c r="K14">
+        <v>146.5</v>
+      </c>
+      <c r="L14">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M14">
+        <v>18.927288</v>
+      </c>
+      <c r="N14">
+        <v>-37.02728799999999</v>
+      </c>
+      <c r="O14">
+        <v>-7.035184719999997</v>
+      </c>
+      <c r="P14">
+        <v>-29.99210327999999</v>
+      </c>
+      <c r="Q14">
+        <v>116.50789672</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08504052612192081</v>
+      </c>
+      <c r="T14">
+        <v>0.6270055610873629</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.1816953384975173</v>
+      </c>
+      <c r="W14">
+        <v>0.2821888468332072</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.9562912552500917</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1106983246072752</v>
+      </c>
+      <c r="C15">
+        <v>293.7236842138128</v>
+      </c>
+      <c r="D15">
+        <v>353.8886842138128</v>
+      </c>
+      <c r="E15">
+        <v>-426.335</v>
+      </c>
+      <c r="F15">
+        <v>85.86500000000001</v>
+      </c>
+      <c r="G15">
+        <v>25.7</v>
+      </c>
+      <c r="H15">
+        <v>148.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>128.4</v>
+      </c>
+      <c r="K15">
+        <v>146.5</v>
+      </c>
+      <c r="L15">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M15">
+        <v>20.504562</v>
+      </c>
+      <c r="N15">
+        <v>-38.604562</v>
+      </c>
+      <c r="O15">
+        <v>-7.334866779999998</v>
+      </c>
+      <c r="P15">
+        <v>-31.26969522</v>
+      </c>
+      <c r="Q15">
+        <v>115.23030478</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08557202642217276</v>
+      </c>
+      <c r="T15">
+        <v>0.6342125215596314</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.1677187739977083</v>
+      </c>
+      <c r="W15">
+        <v>0.2788512432306527</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.882730389461623</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1126983246072752</v>
+      </c>
+      <c r="C16">
+        <v>277.5409654740573</v>
+      </c>
+      <c r="D16">
+        <v>344.3109654740573</v>
+      </c>
+      <c r="E16">
+        <v>-419.73</v>
+      </c>
+      <c r="F16">
+        <v>92.47000000000001</v>
+      </c>
+      <c r="G16">
+        <v>25.7</v>
+      </c>
+      <c r="H16">
+        <v>148.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>128.4</v>
+      </c>
+      <c r="K16">
+        <v>146.5</v>
+      </c>
+      <c r="L16">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M16">
+        <v>22.081836</v>
+      </c>
+      <c r="N16">
+        <v>-40.181836</v>
+      </c>
+      <c r="O16">
+        <v>-7.634548839999997</v>
+      </c>
+      <c r="P16">
+        <v>-32.54728716</v>
+      </c>
+      <c r="Q16">
+        <v>113.95271284</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08611588719452362</v>
+      </c>
+      <c r="T16">
+        <v>0.6415870857638131</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.1557388615693006</v>
+      </c>
+      <c r="W16">
+        <v>0.275990440142749</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.8196782187857927</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1146983246072752</v>
+      </c>
+      <c r="C17">
+        <v>261.8630124871332</v>
+      </c>
+      <c r="D17">
+        <v>335.2380124871332</v>
+      </c>
+      <c r="E17">
+        <v>-413.1250000000001</v>
+      </c>
+      <c r="F17">
+        <v>99.075</v>
+      </c>
+      <c r="G17">
+        <v>25.7</v>
+      </c>
+      <c r="H17">
+        <v>148.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>128.4</v>
+      </c>
+      <c r="K17">
+        <v>146.5</v>
+      </c>
+      <c r="L17">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M17">
+        <v>23.65911</v>
+      </c>
+      <c r="N17">
+        <v>-41.75910999999999</v>
+      </c>
+      <c r="O17">
+        <v>-7.934230899999997</v>
+      </c>
+      <c r="P17">
+        <v>-33.8248791</v>
+      </c>
+      <c r="Q17">
+        <v>112.6751209</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08667254469092978</v>
+      </c>
+      <c r="T17">
+        <v>0.6491351691257404</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.1453562707980139</v>
+      </c>
+      <c r="W17">
+        <v>0.2735110774665657</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.765033004200073</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1166983246072752</v>
+      </c>
+      <c r="C18">
+        <v>246.6509464384797</v>
+      </c>
+      <c r="D18">
+        <v>326.6309464384797</v>
+      </c>
+      <c r="E18">
+        <v>-406.52</v>
+      </c>
+      <c r="F18">
+        <v>105.68</v>
+      </c>
+      <c r="G18">
+        <v>25.7</v>
+      </c>
+      <c r="H18">
+        <v>148.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>128.4</v>
+      </c>
+      <c r="K18">
+        <v>146.5</v>
+      </c>
+      <c r="L18">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M18">
+        <v>25.236384</v>
+      </c>
+      <c r="N18">
+        <v>-43.336384</v>
+      </c>
+      <c r="O18">
+        <v>-8.233912959999996</v>
+      </c>
+      <c r="P18">
+        <v>-35.10247104</v>
+      </c>
+      <c r="Q18">
+        <v>111.39752896</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08724245593725037</v>
+      </c>
+      <c r="T18">
+        <v>0.6568629687581896</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.136271503873138</v>
+      </c>
+      <c r="W18">
+        <v>0.2713416351249053</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.7172184414375684</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1186983246072752</v>
+      </c>
+      <c r="C19">
+        <v>231.8697813425537</v>
+      </c>
+      <c r="D19">
+        <v>318.4547813425538</v>
+      </c>
+      <c r="E19">
+        <v>-399.915</v>
+      </c>
+      <c r="F19">
+        <v>112.285</v>
+      </c>
+      <c r="G19">
+        <v>25.7</v>
+      </c>
+      <c r="H19">
+        <v>148.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>128.4</v>
+      </c>
+      <c r="K19">
+        <v>146.5</v>
+      </c>
+      <c r="L19">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M19">
+        <v>26.813658</v>
+      </c>
+      <c r="N19">
+        <v>-44.913658</v>
+      </c>
+      <c r="O19">
+        <v>-8.533595019999996</v>
+      </c>
+      <c r="P19">
+        <v>-36.38006298000001</v>
+      </c>
+      <c r="Q19">
+        <v>110.11993702</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08782609998468713</v>
+      </c>
+      <c r="T19">
+        <v>0.664776980429975</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.128255533057071</v>
+      </c>
+      <c r="W19">
+        <v>0.2694274212940286</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.6750291213530057</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1206983246072752</v>
+      </c>
+      <c r="C20">
+        <v>217.4879487182082</v>
+      </c>
+      <c r="D20">
+        <v>310.6779487182082</v>
+      </c>
+      <c r="E20">
+        <v>-393.3100000000001</v>
+      </c>
+      <c r="F20">
+        <v>118.89</v>
+      </c>
+      <c r="G20">
+        <v>25.7</v>
+      </c>
+      <c r="H20">
+        <v>148.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>128.4</v>
+      </c>
+      <c r="K20">
+        <v>146.5</v>
+      </c>
+      <c r="L20">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M20">
+        <v>28.390932</v>
+      </c>
+      <c r="N20">
+        <v>-46.490932</v>
+      </c>
+      <c r="O20">
+        <v>-8.833277079999998</v>
+      </c>
+      <c r="P20">
+        <v>-37.65765492</v>
+      </c>
+      <c r="Q20">
+        <v>108.84234508</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08842397925279306</v>
+      </c>
+      <c r="T20">
+        <v>0.6728840167766821</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.1211302256650115</v>
+      </c>
+      <c r="W20">
+        <v>0.2677258978888047</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.6375275035000612</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1226983246072752</v>
+      </c>
+      <c r="C21">
+        <v>203.476890249878</v>
+      </c>
+      <c r="D21">
+        <v>303.271890249878</v>
+      </c>
+      <c r="E21">
+        <v>-386.705</v>
+      </c>
+      <c r="F21">
+        <v>125.495</v>
+      </c>
+      <c r="G21">
+        <v>25.7</v>
+      </c>
+      <c r="H21">
+        <v>148.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>128.4</v>
+      </c>
+      <c r="K21">
+        <v>146.5</v>
+      </c>
+      <c r="L21">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M21">
+        <v>29.968206</v>
+      </c>
+      <c r="N21">
+        <v>-48.068206</v>
+      </c>
+      <c r="O21">
+        <v>-9.132959139999997</v>
+      </c>
+      <c r="P21">
+        <v>-38.93524686</v>
+      </c>
+      <c r="Q21">
+        <v>107.56475314</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08903662097196335</v>
+      </c>
+      <c r="T21">
+        <v>0.6811912268603448</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.1147549506300109</v>
+      </c>
+      <c r="W21">
+        <v>0.2662034822104467</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.6039734243684789</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1246983246072752</v>
+      </c>
+      <c r="C22">
+        <v>189.81070735402</v>
+      </c>
+      <c r="D22">
+        <v>296.21070735402</v>
+      </c>
+      <c r="E22">
+        <v>-380.1</v>
+      </c>
+      <c r="F22">
+        <v>132.1</v>
+      </c>
+      <c r="G22">
+        <v>25.7</v>
+      </c>
+      <c r="H22">
+        <v>148.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>128.4</v>
+      </c>
+      <c r="K22">
+        <v>146.5</v>
+      </c>
+      <c r="L22">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M22">
+        <v>31.54548</v>
+      </c>
+      <c r="N22">
+        <v>-49.64547999999999</v>
+      </c>
+      <c r="O22">
+        <v>-9.432641199999996</v>
+      </c>
+      <c r="P22">
+        <v>-40.2128388</v>
+      </c>
+      <c r="Q22">
+        <v>106.2871612</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08966457873411289</v>
+      </c>
+      <c r="T22">
+        <v>0.6897061171960991</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.1090172030985104</v>
+      </c>
+      <c r="W22">
+        <v>0.2648333080999243</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.5737747531500548</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1266983246072752</v>
+      </c>
+      <c r="C23">
+        <v>176.465858587221</v>
+      </c>
+      <c r="D23">
+        <v>289.470858587221</v>
+      </c>
+      <c r="E23">
+        <v>-373.4950000000001</v>
+      </c>
+      <c r="F23">
+        <v>138.705</v>
+      </c>
+      <c r="G23">
+        <v>25.7</v>
+      </c>
+      <c r="H23">
+        <v>148.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>128.4</v>
+      </c>
+      <c r="K23">
+        <v>146.5</v>
+      </c>
+      <c r="L23">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M23">
+        <v>33.122754</v>
+      </c>
+      <c r="N23">
+        <v>-51.22275399999999</v>
+      </c>
+      <c r="O23">
+        <v>-9.732323259999996</v>
+      </c>
+      <c r="P23">
+        <v>-41.49043074</v>
+      </c>
+      <c r="Q23">
+        <v>105.00956926</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09030843416112697</v>
+      </c>
+      <c r="T23">
+        <v>0.6984365743757965</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.1038259077128671</v>
+      </c>
+      <c r="W23">
+        <v>0.2635936267618327</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.5464521458571951</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1286983246072752</v>
+      </c>
+      <c r="C24">
+        <v>163.4208974455248</v>
+      </c>
+      <c r="D24">
+        <v>283.0308974455248</v>
+      </c>
+      <c r="E24">
+        <v>-366.89</v>
+      </c>
+      <c r="F24">
+        <v>145.31</v>
+      </c>
+      <c r="G24">
+        <v>25.7</v>
+      </c>
+      <c r="H24">
+        <v>148.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>128.4</v>
+      </c>
+      <c r="K24">
+        <v>146.5</v>
+      </c>
+      <c r="L24">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M24">
+        <v>34.700028</v>
+      </c>
+      <c r="N24">
+        <v>-52.800028</v>
+      </c>
+      <c r="O24">
+        <v>-10.03200532</v>
+      </c>
+      <c r="P24">
+        <v>-42.76802268</v>
+      </c>
+      <c r="Q24">
+        <v>103.73197732</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09096879870165425</v>
+      </c>
+      <c r="T24">
+        <v>0.7073908894318965</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.09910654827137308</v>
+      </c>
+      <c r="W24">
+        <v>0.2624666437272039</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.5216134119545954</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1306983246072752</v>
+      </c>
+      <c r="C25">
+        <v>150.6562444016843</v>
+      </c>
+      <c r="D25">
+        <v>276.8712444016843</v>
+      </c>
+      <c r="E25">
+        <v>-360.285</v>
+      </c>
+      <c r="F25">
+        <v>151.915</v>
+      </c>
+      <c r="G25">
+        <v>25.7</v>
+      </c>
+      <c r="H25">
+        <v>148.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>128.4</v>
+      </c>
+      <c r="K25">
+        <v>146.5</v>
+      </c>
+      <c r="L25">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M25">
+        <v>36.27730200000001</v>
+      </c>
+      <c r="N25">
+        <v>-54.377302</v>
+      </c>
+      <c r="O25">
+        <v>-10.33168738</v>
+      </c>
+      <c r="P25">
+        <v>-44.04561462</v>
+      </c>
+      <c r="Q25">
+        <v>102.45438538</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.0916463155679095</v>
+      </c>
+      <c r="T25">
+        <v>0.7165777840998433</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.09479756791174816</v>
+      </c>
+      <c r="W25">
+        <v>0.2614376592173255</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.4989345679565693</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1326983246072752</v>
+      </c>
+      <c r="C26">
+        <v>138.1539880755532</v>
+      </c>
+      <c r="D26">
+        <v>270.9739880755532</v>
+      </c>
+      <c r="E26">
+        <v>-353.6800000000001</v>
+      </c>
+      <c r="F26">
+        <v>158.52</v>
+      </c>
+      <c r="G26">
+        <v>25.7</v>
+      </c>
+      <c r="H26">
+        <v>148.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>128.4</v>
+      </c>
+      <c r="K26">
+        <v>146.5</v>
+      </c>
+      <c r="L26">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M26">
+        <v>37.85457599999999</v>
+      </c>
+      <c r="N26">
+        <v>-55.95457599999999</v>
+      </c>
+      <c r="O26">
+        <v>-10.63136943999999</v>
+      </c>
+      <c r="P26">
+        <v>-45.32320656</v>
+      </c>
+      <c r="Q26">
+        <v>101.17679344</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09234166182538199</v>
+      </c>
+      <c r="T26">
+        <v>0.7260064391537886</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.09084766924875867</v>
+      </c>
+      <c r="W26">
+        <v>0.2604944234166036</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.4781456276250458</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1346983246072752</v>
+      </c>
+      <c r="C27">
+        <v>125.89771128453</v>
+      </c>
+      <c r="D27">
+        <v>265.32271128453</v>
+      </c>
+      <c r="E27">
+        <v>-347.075</v>
+      </c>
+      <c r="F27">
+        <v>165.125</v>
+      </c>
+      <c r="G27">
+        <v>25.7</v>
+      </c>
+      <c r="H27">
+        <v>148.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>128.4</v>
+      </c>
+      <c r="K27">
+        <v>146.5</v>
+      </c>
+      <c r="L27">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M27">
+        <v>39.43185</v>
+      </c>
+      <c r="N27">
+        <v>-57.53185</v>
+      </c>
+      <c r="O27">
+        <v>-10.9310515</v>
+      </c>
+      <c r="P27">
+        <v>-46.6007985</v>
+      </c>
+      <c r="Q27">
+        <v>99.8992015</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.0930555506497204</v>
+      </c>
+      <c r="T27">
+        <v>0.7356865250091723</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.08721376247880831</v>
+      </c>
+      <c r="W27">
+        <v>0.2596266464799394</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.4590198025200438</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1366983246072752</v>
+      </c>
+      <c r="C28">
+        <v>113.8723384160688</v>
+      </c>
+      <c r="D28">
+        <v>259.9023384160689</v>
+      </c>
+      <c r="E28">
+        <v>-340.47</v>
+      </c>
+      <c r="F28">
+        <v>171.73</v>
+      </c>
+      <c r="G28">
+        <v>25.7</v>
+      </c>
+      <c r="H28">
+        <v>148.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>128.4</v>
+      </c>
+      <c r="K28">
+        <v>146.5</v>
+      </c>
+      <c r="L28">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M28">
+        <v>41.00912400000001</v>
+      </c>
+      <c r="N28">
+        <v>-59.109124</v>
+      </c>
+      <c r="O28">
+        <v>-11.23073356</v>
+      </c>
+      <c r="P28">
+        <v>-47.87839044</v>
+      </c>
+      <c r="Q28">
+        <v>98.62160956</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09378873376660854</v>
+      </c>
+      <c r="T28">
+        <v>0.7456282348065937</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.08385938699885413</v>
+      </c>
+      <c r="W28">
+        <v>0.2588256216153264</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.4413651947308115</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1386983246072752</v>
+      </c>
+      <c r="C29">
+        <v>102.0640011341313</v>
+      </c>
+      <c r="D29">
+        <v>254.6990011341313</v>
+      </c>
+      <c r="E29">
+        <v>-333.865</v>
+      </c>
+      <c r="F29">
+        <v>178.335</v>
+      </c>
+      <c r="G29">
+        <v>25.7</v>
+      </c>
+      <c r="H29">
+        <v>148.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>128.4</v>
+      </c>
+      <c r="K29">
+        <v>146.5</v>
+      </c>
+      <c r="L29">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M29">
+        <v>42.586398</v>
+      </c>
+      <c r="N29">
+        <v>-60.686398</v>
+      </c>
+      <c r="O29">
+        <v>-11.53041562</v>
+      </c>
+      <c r="P29">
+        <v>-49.15598238</v>
+      </c>
+      <c r="Q29">
+        <v>97.34401762</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09454200409217851</v>
+      </c>
+      <c r="T29">
+        <v>0.7558423202149032</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.08075348377667436</v>
+      </c>
+      <c r="W29">
+        <v>0.2580839319258699</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.4250183356667072</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1406983246072752</v>
+      </c>
+      <c r="C30">
+        <v>90.45991990064178</v>
+      </c>
+      <c r="D30">
+        <v>249.6999199006418</v>
+      </c>
+      <c r="E30">
+        <v>-327.26</v>
+      </c>
+      <c r="F30">
+        <v>184.94</v>
+      </c>
+      <c r="G30">
+        <v>25.7</v>
+      </c>
+      <c r="H30">
+        <v>148.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>128.4</v>
+      </c>
+      <c r="K30">
+        <v>146.5</v>
+      </c>
+      <c r="L30">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M30">
+        <v>44.16367200000001</v>
+      </c>
+      <c r="N30">
+        <v>-62.263672</v>
+      </c>
+      <c r="O30">
+        <v>-11.83009768</v>
+      </c>
+      <c r="P30">
+        <v>-50.43357432000001</v>
+      </c>
+      <c r="Q30">
+        <v>96.06642567999999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09531619859345877</v>
+      </c>
+      <c r="T30">
+        <v>0.7663401302178879</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.07786943078465028</v>
+      </c>
+      <c r="W30">
+        <v>0.2573952200713745</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.4098391093928964</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1426983246072752</v>
+      </c>
+      <c r="C31">
+        <v>79.04829918092409</v>
+      </c>
+      <c r="D31">
+        <v>244.8932991809241</v>
+      </c>
+      <c r="E31">
+        <v>-320.6550000000001</v>
+      </c>
+      <c r="F31">
+        <v>191.545</v>
+      </c>
+      <c r="G31">
+        <v>25.7</v>
+      </c>
+      <c r="H31">
+        <v>148.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>128.4</v>
+      </c>
+      <c r="K31">
+        <v>146.5</v>
+      </c>
+      <c r="L31">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M31">
+        <v>45.740946</v>
+      </c>
+      <c r="N31">
+        <v>-63.840946</v>
+      </c>
+      <c r="O31">
+        <v>-12.12977974</v>
+      </c>
+      <c r="P31">
+        <v>-51.71116626</v>
+      </c>
+      <c r="Q31">
+        <v>94.78883374</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09611220139054974</v>
+      </c>
+      <c r="T31">
+        <v>0.7771336531787033</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.07518427799897269</v>
+      </c>
+      <c r="W31">
+        <v>0.2567540055861547</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.3957067263103826</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1446983246072752</v>
+      </c>
+      <c r="C32">
+        <v>67.81823452406357</v>
+      </c>
+      <c r="D32">
+        <v>240.2682345240636</v>
+      </c>
+      <c r="E32">
+        <v>-314.0500000000001</v>
+      </c>
+      <c r="F32">
+        <v>198.15</v>
+      </c>
+      <c r="G32">
+        <v>25.7</v>
+      </c>
+      <c r="H32">
+        <v>148.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>128.4</v>
+      </c>
+      <c r="K32">
+        <v>146.5</v>
+      </c>
+      <c r="L32">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M32">
+        <v>47.31822</v>
+      </c>
+      <c r="N32">
+        <v>-65.41821999999999</v>
+      </c>
+      <c r="O32">
+        <v>-12.4294618</v>
+      </c>
+      <c r="P32">
+        <v>-52.98875819999999</v>
+      </c>
+      <c r="Q32">
+        <v>93.51124180000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09693094712470043</v>
+      </c>
+      <c r="T32">
+        <v>0.7882355625098275</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.07267813539900693</v>
+      </c>
+      <c r="W32">
+        <v>0.2561555387332828</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.3825165021000365</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1466983246072752</v>
+      </c>
+      <c r="C33">
+        <v>56.75962997740203</v>
+      </c>
+      <c r="D33">
+        <v>235.814629977402</v>
+      </c>
+      <c r="E33">
+        <v>-307.4450000000001</v>
+      </c>
+      <c r="F33">
+        <v>204.755</v>
+      </c>
+      <c r="G33">
+        <v>25.7</v>
+      </c>
+      <c r="H33">
+        <v>148.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>128.4</v>
+      </c>
+      <c r="K33">
+        <v>146.5</v>
+      </c>
+      <c r="L33">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M33">
+        <v>48.895494</v>
+      </c>
+      <c r="N33">
+        <v>-66.99549399999999</v>
+      </c>
+      <c r="O33">
+        <v>-12.72914386</v>
+      </c>
+      <c r="P33">
+        <v>-54.26635014</v>
+      </c>
+      <c r="Q33">
+        <v>92.23364986</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09777342461926132</v>
+      </c>
+      <c r="T33">
+        <v>0.7996592663143178</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.0703336794183938</v>
+      </c>
+      <c r="W33">
+        <v>0.2555956826451125</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.3701772600968096</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1486983246072752</v>
+      </c>
+      <c r="C34">
+        <v>45.8631245186956</v>
+      </c>
+      <c r="D34">
+        <v>231.5231245186956</v>
+      </c>
+      <c r="E34">
+        <v>-300.84</v>
+      </c>
+      <c r="F34">
+        <v>211.36</v>
+      </c>
+      <c r="G34">
+        <v>25.7</v>
+      </c>
+      <c r="H34">
+        <v>148.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>128.4</v>
+      </c>
+      <c r="K34">
+        <v>146.5</v>
+      </c>
+      <c r="L34">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M34">
+        <v>50.47276800000001</v>
+      </c>
+      <c r="N34">
+        <v>-68.572768</v>
+      </c>
+      <c r="O34">
+        <v>-13.02882592</v>
+      </c>
+      <c r="P34">
+        <v>-55.54394208</v>
+      </c>
+      <c r="Q34">
+        <v>90.95605792000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09864068086366223</v>
+      </c>
+      <c r="T34">
+        <v>0.8114189614071755</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.068135751936569</v>
+      </c>
+      <c r="W34">
+        <v>0.2550708175624527</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.3586092207187841</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1506983246072752</v>
+      </c>
+      <c r="C35">
+        <v>35.12002637770442</v>
+      </c>
+      <c r="D35">
+        <v>227.3850263777044</v>
+      </c>
+      <c r="E35">
+        <v>-294.235</v>
+      </c>
+      <c r="F35">
+        <v>217.965</v>
+      </c>
+      <c r="G35">
+        <v>25.7</v>
+      </c>
+      <c r="H35">
+        <v>148.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>128.4</v>
+      </c>
+      <c r="K35">
+        <v>146.5</v>
+      </c>
+      <c r="L35">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M35">
+        <v>52.050042</v>
+      </c>
+      <c r="N35">
+        <v>-70.150042</v>
+      </c>
+      <c r="O35">
+        <v>-13.32850798</v>
+      </c>
+      <c r="P35">
+        <v>-56.82153402</v>
+      </c>
+      <c r="Q35">
+        <v>89.67846598</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09953382535416466</v>
+      </c>
+      <c r="T35">
+        <v>0.8235296921744468</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.0660710321809154</v>
+      </c>
+      <c r="W35">
+        <v>0.2545777624848026</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.347742274636397</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1526983246072752</v>
+      </c>
+      <c r="C36">
+        <v>24.52225427746967</v>
+      </c>
+      <c r="D36">
+        <v>223.3922542774697</v>
+      </c>
+      <c r="E36">
+        <v>-287.63</v>
+      </c>
+      <c r="F36">
+        <v>224.57</v>
+      </c>
+      <c r="G36">
+        <v>25.7</v>
+      </c>
+      <c r="H36">
+        <v>148.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>128.4</v>
+      </c>
+      <c r="K36">
+        <v>146.5</v>
+      </c>
+      <c r="L36">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M36">
+        <v>53.62731600000001</v>
+      </c>
+      <c r="N36">
+        <v>-71.727316</v>
+      </c>
+      <c r="O36">
+        <v>-13.62819004</v>
+      </c>
+      <c r="P36">
+        <v>-58.09912596000001</v>
+      </c>
+      <c r="Q36">
+        <v>88.40087403999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1004540348292278</v>
+      </c>
+      <c r="T36">
+        <v>0.8360074147831505</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.06412776652853552</v>
+      </c>
+      <c r="W36">
+        <v>0.2541137106470143</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.3375145606765029</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1546983246072752</v>
+      </c>
+      <c r="C37">
+        <v>14.06228475941253</v>
+      </c>
+      <c r="D37">
+        <v>219.5372847594126</v>
+      </c>
+      <c r="E37">
+        <v>-281.025</v>
+      </c>
+      <c r="F37">
+        <v>231.175</v>
+      </c>
+      <c r="G37">
+        <v>25.7</v>
+      </c>
+      <c r="H37">
+        <v>148.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>128.4</v>
+      </c>
+      <c r="K37">
+        <v>146.5</v>
+      </c>
+      <c r="L37">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M37">
+        <v>55.20459</v>
+      </c>
+      <c r="N37">
+        <v>-73.30458999999999</v>
+      </c>
+      <c r="O37">
+        <v>-13.92787209999999</v>
+      </c>
+      <c r="P37">
+        <v>-59.3767179</v>
+      </c>
+      <c r="Q37">
+        <v>87.12328210000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1014025584419851</v>
+      </c>
+      <c r="T37">
+        <v>0.8488690673182758</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.06229554462772023</v>
+      </c>
+      <c r="W37">
+        <v>0.2536761760570996</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.327871287514317</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1566983246072752</v>
+      </c>
+      <c r="C38">
+        <v>3.733104869822085</v>
+      </c>
+      <c r="D38">
+        <v>215.8131048698221</v>
+      </c>
+      <c r="E38">
+        <v>-274.4200000000001</v>
+      </c>
+      <c r="F38">
+        <v>237.78</v>
+      </c>
+      <c r="G38">
+        <v>25.7</v>
+      </c>
+      <c r="H38">
+        <v>148.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>128.4</v>
+      </c>
+      <c r="K38">
+        <v>146.5</v>
+      </c>
+      <c r="L38">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M38">
+        <v>56.78186400000001</v>
+      </c>
+      <c r="N38">
+        <v>-74.88186400000001</v>
+      </c>
+      <c r="O38">
+        <v>-14.22755416</v>
+      </c>
+      <c r="P38">
+        <v>-60.65430984000001</v>
+      </c>
+      <c r="Q38">
+        <v>85.84569015999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1023807234176411</v>
+      </c>
+      <c r="T38">
+        <v>0.8621326464951239</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.06056511283250577</v>
+      </c>
+      <c r="W38">
+        <v>0.2532629489444024</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.3187637517500306</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1586983246072752</v>
+      </c>
+      <c r="C39">
+        <v>-6.471830418293337</v>
+      </c>
+      <c r="D39">
+        <v>212.2131695817067</v>
+      </c>
+      <c r="E39">
+        <v>-267.8150000000001</v>
+      </c>
+      <c r="F39">
+        <v>244.385</v>
+      </c>
+      <c r="G39">
+        <v>25.7</v>
+      </c>
+      <c r="H39">
+        <v>148.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>128.4</v>
+      </c>
+      <c r="K39">
+        <v>146.5</v>
+      </c>
+      <c r="L39">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M39">
+        <v>58.359138</v>
+      </c>
+      <c r="N39">
+        <v>-76.459138</v>
+      </c>
+      <c r="O39">
+        <v>-14.52723622</v>
+      </c>
+      <c r="P39">
+        <v>-61.93190178</v>
+      </c>
+      <c r="Q39">
+        <v>84.56809822</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1033899412496672</v>
+      </c>
+      <c r="T39">
+        <v>0.8758172916775862</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.0589282178910867</v>
+      </c>
+      <c r="W39">
+        <v>0.2528720584323915</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.310148515216246</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1606983246072752</v>
+      </c>
+      <c r="C40">
+        <v>-16.55863659184661</v>
+      </c>
+      <c r="D40">
+        <v>208.7313634081534</v>
+      </c>
+      <c r="E40">
+        <v>-261.21</v>
+      </c>
+      <c r="F40">
+        <v>250.99</v>
+      </c>
+      <c r="G40">
+        <v>25.7</v>
+      </c>
+      <c r="H40">
+        <v>148.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>128.4</v>
+      </c>
+      <c r="K40">
+        <v>146.5</v>
+      </c>
+      <c r="L40">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M40">
+        <v>59.936412</v>
+      </c>
+      <c r="N40">
+        <v>-78.036412</v>
+      </c>
+      <c r="O40">
+        <v>-14.82691828</v>
+      </c>
+      <c r="P40">
+        <v>-63.20949372</v>
+      </c>
+      <c r="Q40">
+        <v>83.29050627999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1044317144956295</v>
+      </c>
+      <c r="T40">
+        <v>0.8899433770272247</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.05737747531500547</v>
+      </c>
+      <c r="W40">
+        <v>0.2525017411052233</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.3019867121842394</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1626983246072752</v>
+      </c>
+      <c r="C41">
+        <v>-26.53303426642822</v>
+      </c>
+      <c r="D41">
+        <v>205.3619657335718</v>
+      </c>
+      <c r="E41">
+        <v>-254.605</v>
+      </c>
+      <c r="F41">
+        <v>257.595</v>
+      </c>
+      <c r="G41">
+        <v>25.7</v>
+      </c>
+      <c r="H41">
+        <v>148.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>128.4</v>
+      </c>
+      <c r="K41">
+        <v>146.5</v>
+      </c>
+      <c r="L41">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M41">
+        <v>61.51368600000001</v>
+      </c>
+      <c r="N41">
+        <v>-79.613686</v>
+      </c>
+      <c r="O41">
+        <v>-15.12660034</v>
+      </c>
+      <c r="P41">
+        <v>-64.48708566000001</v>
+      </c>
+      <c r="Q41">
+        <v>82.01291433999999</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1055076442414595</v>
+      </c>
+      <c r="T41">
+        <v>0.9045326127161956</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.0559062579992361</v>
+      </c>
+      <c r="W41">
+        <v>0.2521504144102176</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.2942434631538742</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1646983246072752</v>
+      </c>
+      <c r="C42">
+        <v>-36.4003805506091</v>
+      </c>
+      <c r="D42">
+        <v>202.0996194493909</v>
+      </c>
+      <c r="E42">
+        <v>-248.0000000000001</v>
+      </c>
+      <c r="F42">
+        <v>264.2</v>
+      </c>
+      <c r="G42">
+        <v>25.7</v>
+      </c>
+      <c r="H42">
+        <v>148.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>128.4</v>
+      </c>
+      <c r="K42">
+        <v>146.5</v>
+      </c>
+      <c r="L42">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M42">
+        <v>63.09096</v>
+      </c>
+      <c r="N42">
+        <v>-81.19095999999999</v>
+      </c>
+      <c r="O42">
+        <v>-15.42628239999999</v>
+      </c>
+      <c r="P42">
+        <v>-65.7646776</v>
+      </c>
+      <c r="Q42">
+        <v>80.7353224</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1066194383121505</v>
+      </c>
+      <c r="T42">
+        <v>0.9196081562614655</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.0545086015492552</v>
+      </c>
+      <c r="W42">
+        <v>0.2518166540499622</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.2868873765750273</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1666983246072752</v>
+      </c>
+      <c r="C43">
+        <v>-46.16569746750318</v>
+      </c>
+      <c r="D43">
+        <v>198.9393025324968</v>
+      </c>
+      <c r="E43">
+        <v>-241.395</v>
+      </c>
+      <c r="F43">
+        <v>270.805</v>
+      </c>
+      <c r="G43">
+        <v>25.7</v>
+      </c>
+      <c r="H43">
+        <v>148.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>128.4</v>
+      </c>
+      <c r="K43">
+        <v>146.5</v>
+      </c>
+      <c r="L43">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M43">
+        <v>64.668234</v>
+      </c>
+      <c r="N43">
+        <v>-82.76823399999999</v>
+      </c>
+      <c r="O43">
+        <v>-15.72596445999999</v>
+      </c>
+      <c r="P43">
+        <v>-67.04226953999999</v>
+      </c>
+      <c r="Q43">
+        <v>79.45773046000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1077689203174412</v>
+      </c>
+      <c r="T43">
+        <v>0.9351947351811514</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.053179123462688</v>
+      </c>
+      <c r="W43">
+        <v>0.2514991746828899</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.2798901234878317</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1686983246072752</v>
+      </c>
+      <c r="C44">
+        <v>-55.83369775074706</v>
+      </c>
+      <c r="D44">
+        <v>195.8763022492529</v>
+      </c>
+      <c r="E44">
+        <v>-234.7900000000001</v>
+      </c>
+      <c r="F44">
+        <v>277.41</v>
+      </c>
+      <c r="G44">
+        <v>25.7</v>
+      </c>
+      <c r="H44">
+        <v>148.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>128.4</v>
+      </c>
+      <c r="K44">
+        <v>146.5</v>
+      </c>
+      <c r="L44">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M44">
+        <v>66.245508</v>
+      </c>
+      <c r="N44">
+        <v>-84.345508</v>
+      </c>
+      <c r="O44">
+        <v>-16.02564652</v>
+      </c>
+      <c r="P44">
+        <v>-68.31986148</v>
+      </c>
+      <c r="Q44">
+        <v>78.18013852</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1089580396332591</v>
+      </c>
+      <c r="T44">
+        <v>0.9513187823394469</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.05191295385643353</v>
+      </c>
+      <c r="W44">
+        <v>0.2511968133809164</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.2732260729285976</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1706983246072752</v>
+      </c>
+      <c r="C45">
+        <v>-65.40880829358332</v>
+      </c>
+      <c r="D45">
+        <v>192.9061917064167</v>
+      </c>
+      <c r="E45">
+        <v>-228.1850000000001</v>
+      </c>
+      <c r="F45">
+        <v>284.015</v>
+      </c>
+      <c r="G45">
+        <v>25.7</v>
+      </c>
+      <c r="H45">
+        <v>148.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>128.4</v>
+      </c>
+      <c r="K45">
+        <v>146.5</v>
+      </c>
+      <c r="L45">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M45">
+        <v>67.822782</v>
+      </c>
+      <c r="N45">
+        <v>-85.922782</v>
+      </c>
+      <c r="O45">
+        <v>-16.32532857999999</v>
+      </c>
+      <c r="P45">
+        <v>-69.59745342000001</v>
+      </c>
+      <c r="Q45">
+        <v>76.90254657999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1101888824338426</v>
+      </c>
+      <c r="T45">
+        <v>0.9680085855383846</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.05070567585977227</v>
+      </c>
+      <c r="W45">
+        <v>0.2509085153953137</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.2668719782093278</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1726983246072752</v>
+      </c>
+      <c r="C46">
+        <v>-74.89519149643093</v>
+      </c>
+      <c r="D46">
+        <v>190.0248085035691</v>
+      </c>
+      <c r="E46">
+        <v>-221.58</v>
+      </c>
+      <c r="F46">
+        <v>290.62</v>
+      </c>
+      <c r="G46">
+        <v>25.7</v>
+      </c>
+      <c r="H46">
+        <v>148.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>128.4</v>
+      </c>
+      <c r="K46">
+        <v>146.5</v>
+      </c>
+      <c r="L46">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M46">
+        <v>69.40005600000001</v>
+      </c>
+      <c r="N46">
+        <v>-87.500056</v>
+      </c>
+      <c r="O46">
+        <v>-16.62501064</v>
+      </c>
+      <c r="P46">
+        <v>-70.87504536</v>
+      </c>
+      <c r="Q46">
+        <v>75.62495464</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1114636839058755</v>
+      </c>
+      <c r="T46">
+        <v>0.9852944531372844</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.04955327413568654</v>
+      </c>
+      <c r="W46">
+        <v>0.250633321863602</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.2608067059772976</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1746983246072752</v>
+      </c>
+      <c r="C47">
+        <v>-84.29676472943746</v>
+      </c>
+      <c r="D47">
+        <v>187.2282352705626</v>
+      </c>
+      <c r="E47">
+        <v>-214.975</v>
+      </c>
+      <c r="F47">
+        <v>297.225</v>
+      </c>
+      <c r="G47">
+        <v>25.7</v>
+      </c>
+      <c r="H47">
+        <v>148.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>128.4</v>
+      </c>
+      <c r="K47">
+        <v>146.5</v>
+      </c>
+      <c r="L47">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M47">
+        <v>70.97733000000001</v>
+      </c>
+      <c r="N47">
+        <v>-89.07733</v>
+      </c>
+      <c r="O47">
+        <v>-16.92469269999999</v>
+      </c>
+      <c r="P47">
+        <v>-72.15263730000001</v>
+      </c>
+      <c r="Q47">
+        <v>74.34736269999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1127848417950733</v>
+      </c>
+      <c r="T47">
+        <v>1.003208897739781</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.04845209026600462</v>
+      </c>
+      <c r="W47">
+        <v>0.2503703591555219</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.2550110014000244</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1766983246072752</v>
+      </c>
+      <c r="C48">
+        <v>-93.61721810138781</v>
+      </c>
+      <c r="D48">
+        <v>184.5127818986122</v>
+      </c>
+      <c r="E48">
+        <v>-208.37</v>
+      </c>
+      <c r="F48">
+        <v>303.83</v>
+      </c>
+      <c r="G48">
+        <v>25.7</v>
+      </c>
+      <c r="H48">
+        <v>148.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>128.4</v>
+      </c>
+      <c r="K48">
+        <v>146.5</v>
+      </c>
+      <c r="L48">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M48">
+        <v>72.55460400000001</v>
+      </c>
+      <c r="N48">
+        <v>-90.65460400000001</v>
+      </c>
+      <c r="O48">
+        <v>-17.22437476</v>
+      </c>
+      <c r="P48">
+        <v>-73.43022924000002</v>
+      </c>
+      <c r="Q48">
+        <v>73.06977075999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.114154931457945</v>
+      </c>
+      <c r="T48">
+        <v>1.021786840290517</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.04739878395587408</v>
+      </c>
+      <c r="W48">
+        <v>0.2501188296086627</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.2494672839782848</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1786983246072752</v>
+      </c>
+      <c r="C49">
+        <v>-102.8600307044562</v>
+      </c>
+      <c r="D49">
+        <v>181.8749692955438</v>
+      </c>
+      <c r="E49">
+        <v>-201.765</v>
+      </c>
+      <c r="F49">
+        <v>310.435</v>
+      </c>
+      <c r="G49">
+        <v>25.7</v>
+      </c>
+      <c r="H49">
+        <v>148.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>128.4</v>
+      </c>
+      <c r="K49">
+        <v>146.5</v>
+      </c>
+      <c r="L49">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M49">
+        <v>74.131878</v>
+      </c>
+      <c r="N49">
+        <v>-92.23187799999999</v>
+      </c>
+      <c r="O49">
+        <v>-17.52405681999999</v>
+      </c>
+      <c r="P49">
+        <v>-74.70782118</v>
+      </c>
+      <c r="Q49">
+        <v>71.79217882</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1155767226175289</v>
+      </c>
+      <c r="T49">
+        <v>1.041065837277131</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.04639029919085549</v>
+      </c>
+      <c r="W49">
+        <v>0.2498780034467763</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.2441594694255553</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1806983246072752</v>
+      </c>
+      <c r="C50">
+        <v>-112.028485485179</v>
+      </c>
+      <c r="D50">
+        <v>179.311514514821</v>
+      </c>
+      <c r="E50">
+        <v>-195.1600000000001</v>
+      </c>
+      <c r="F50">
+        <v>317.04</v>
+      </c>
+      <c r="G50">
+        <v>25.7</v>
+      </c>
+      <c r="H50">
+        <v>148.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>128.4</v>
+      </c>
+      <c r="K50">
+        <v>146.5</v>
+      </c>
+      <c r="L50">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M50">
+        <v>75.70915199999999</v>
+      </c>
+      <c r="N50">
+        <v>-93.80915199999998</v>
+      </c>
+      <c r="O50">
+        <v>-17.82373887999999</v>
+      </c>
+      <c r="P50">
+        <v>-75.98541311999999</v>
+      </c>
+      <c r="Q50">
+        <v>70.51458688000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1170531980524814</v>
+      </c>
+      <c r="T50">
+        <v>1.061086334147845</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.04542383462437934</v>
+      </c>
+      <c r="W50">
+        <v>0.2496472117083018</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.2390728138125229</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1826983246072752</v>
+      </c>
+      <c r="C51">
+        <v>-121.1256828753042</v>
+      </c>
+      <c r="D51">
+        <v>176.8193171246957</v>
+      </c>
+      <c r="E51">
+        <v>-188.5550000000001</v>
+      </c>
+      <c r="F51">
+        <v>323.645</v>
+      </c>
+      <c r="G51">
+        <v>25.7</v>
+      </c>
+      <c r="H51">
+        <v>148.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>128.4</v>
+      </c>
+      <c r="K51">
+        <v>146.5</v>
+      </c>
+      <c r="L51">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M51">
+        <v>77.28642600000001</v>
+      </c>
+      <c r="N51">
+        <v>-95.386426</v>
+      </c>
+      <c r="O51">
+        <v>-18.12342094</v>
+      </c>
+      <c r="P51">
+        <v>-77.26300506000001</v>
+      </c>
+      <c r="Q51">
+        <v>69.23699493999999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.118587574484883</v>
+      </c>
+      <c r="T51">
+        <v>1.081891948542901</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.04449681759122873</v>
+      </c>
+      <c r="W51">
+        <v>0.2494258400407854</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.2341937767959408</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1846983246072752</v>
+      </c>
+      <c r="C52">
+        <v>-130.1545533015158</v>
+      </c>
+      <c r="D52">
+        <v>174.3954466984842</v>
+      </c>
+      <c r="E52">
+        <v>-181.95</v>
+      </c>
+      <c r="F52">
+        <v>330.25</v>
+      </c>
+      <c r="G52">
+        <v>25.7</v>
+      </c>
+      <c r="H52">
+        <v>148.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>128.4</v>
+      </c>
+      <c r="K52">
+        <v>146.5</v>
+      </c>
+      <c r="L52">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M52">
+        <v>78.86370000000001</v>
+      </c>
+      <c r="N52">
+        <v>-96.9637</v>
+      </c>
+      <c r="O52">
+        <v>-18.42310299999999</v>
+      </c>
+      <c r="P52">
+        <v>-78.54059700000001</v>
+      </c>
+      <c r="Q52">
+        <v>67.95940299999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1201833259745806</v>
+      </c>
+      <c r="T52">
+        <v>1.103529787513759</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.04360688123940416</v>
+      </c>
+      <c r="W52">
+        <v>0.2492133232399697</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.2295099012600219</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1866983246072751</v>
+      </c>
+      <c r="C53">
+        <v>-139.1178686801594</v>
+      </c>
+      <c r="D53">
+        <v>172.0371313198406</v>
+      </c>
+      <c r="E53">
+        <v>-175.345</v>
+      </c>
+      <c r="F53">
+        <v>336.855</v>
+      </c>
+      <c r="G53">
+        <v>25.7</v>
+      </c>
+      <c r="H53">
+        <v>148.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>128.4</v>
+      </c>
+      <c r="K53">
+        <v>146.5</v>
+      </c>
+      <c r="L53">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M53">
+        <v>80.44097400000001</v>
+      </c>
+      <c r="N53">
+        <v>-98.54097400000001</v>
+      </c>
+      <c r="O53">
+        <v>-18.72278506</v>
+      </c>
+      <c r="P53">
+        <v>-79.81818894000001</v>
+      </c>
+      <c r="Q53">
+        <v>66.68181105999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1218442101781435</v>
+      </c>
+      <c r="T53">
+        <v>1.126050803585468</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.04275184435235702</v>
+      </c>
+      <c r="W53">
+        <v>0.2490091404313428</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.2250097071176687</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1886983246072752</v>
+      </c>
+      <c r="C54">
+        <v>-148.0182529917664</v>
+      </c>
+      <c r="D54">
+        <v>169.7417470082337</v>
+      </c>
+      <c r="E54">
+        <v>-168.74</v>
+      </c>
+      <c r="F54">
+        <v>343.46</v>
+      </c>
+      <c r="G54">
+        <v>25.7</v>
+      </c>
+      <c r="H54">
+        <v>148.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>128.4</v>
+      </c>
+      <c r="K54">
+        <v>146.5</v>
+      </c>
+      <c r="L54">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M54">
+        <v>82.01824800000001</v>
+      </c>
+      <c r="N54">
+        <v>-100.118248</v>
+      </c>
+      <c r="O54">
+        <v>-19.02246711999999</v>
+      </c>
+      <c r="P54">
+        <v>-81.09578088000001</v>
+      </c>
+      <c r="Q54">
+        <v>65.40421911999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1235742978901882</v>
+      </c>
+      <c r="T54">
+        <v>1.149510195326832</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.04192969349942707</v>
+      </c>
+      <c r="W54">
+        <v>0.2488128108076632</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.2206825973654056</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1906983246072752</v>
+      </c>
+      <c r="C55">
+        <v>-156.8581920201866</v>
+      </c>
+      <c r="D55">
+        <v>167.5068079798134</v>
+      </c>
+      <c r="E55">
+        <v>-162.135</v>
+      </c>
+      <c r="F55">
+        <v>350.065</v>
+      </c>
+      <c r="G55">
+        <v>25.7</v>
+      </c>
+      <c r="H55">
+        <v>148.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>128.4</v>
+      </c>
+      <c r="K55">
+        <v>146.5</v>
+      </c>
+      <c r="L55">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M55">
+        <v>83.595522</v>
+      </c>
+      <c r="N55">
+        <v>-101.695522</v>
+      </c>
+      <c r="O55">
+        <v>-19.32214917999999</v>
+      </c>
+      <c r="P55">
+        <v>-82.37337282</v>
+      </c>
+      <c r="Q55">
+        <v>64.12662718</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1253780063559368</v>
+      </c>
+      <c r="T55">
+        <v>1.17396785905719</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.04113856720698505</v>
+      </c>
+      <c r="W55">
+        <v>0.2486238898490281</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.2165187747736057</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1926983246072752</v>
+      </c>
+      <c r="C56">
+        <v>-165.6400423323296</v>
+      </c>
+      <c r="D56">
+        <v>165.3299576676704</v>
+      </c>
+      <c r="E56">
+        <v>-155.53</v>
+      </c>
+      <c r="F56">
+        <v>356.67</v>
+      </c>
+      <c r="G56">
+        <v>25.7</v>
+      </c>
+      <c r="H56">
+        <v>148.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>128.4</v>
+      </c>
+      <c r="K56">
+        <v>146.5</v>
+      </c>
+      <c r="L56">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M56">
+        <v>85.17279600000001</v>
+      </c>
+      <c r="N56">
+        <v>-103.272796</v>
+      </c>
+      <c r="O56">
+        <v>-19.62183124</v>
+      </c>
+      <c r="P56">
+        <v>-83.65096476000001</v>
+      </c>
+      <c r="Q56">
+        <v>62.84903523999999</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.127260136928892</v>
+      </c>
+      <c r="T56">
+        <v>1.199488899471477</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.04037674188833718</v>
+      </c>
+      <c r="W56">
+        <v>0.2484419659629349</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.2125091678333537</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1946983246072752</v>
+      </c>
+      <c r="C57">
+        <v>-174.3660395667022</v>
+      </c>
+      <c r="D57">
+        <v>163.2089604332978</v>
+      </c>
+      <c r="E57">
+        <v>-148.925</v>
+      </c>
+      <c r="F57">
+        <v>363.275</v>
+      </c>
+      <c r="G57">
+        <v>25.7</v>
+      </c>
+      <c r="H57">
+        <v>148.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>128.4</v>
+      </c>
+      <c r="K57">
+        <v>146.5</v>
+      </c>
+      <c r="L57">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M57">
+        <v>86.75007000000001</v>
+      </c>
+      <c r="N57">
+        <v>-104.85007</v>
+      </c>
+      <c r="O57">
+        <v>-19.92151329999999</v>
+      </c>
+      <c r="P57">
+        <v>-84.9285567</v>
+      </c>
+      <c r="Q57">
+        <v>61.5714433</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.129225917749534</v>
+      </c>
+      <c r="T57">
+        <v>1.226144208348621</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.03964261930854923</v>
+      </c>
+      <c r="W57">
+        <v>0.2482666574908816</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.208645364781838</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1966983246072752</v>
+      </c>
+      <c r="C58">
+        <v>-183.038306092034</v>
+      </c>
+      <c r="D58">
+        <v>161.141693907966</v>
+      </c>
+      <c r="E58">
+        <v>-142.32</v>
+      </c>
+      <c r="F58">
+        <v>369.8800000000001</v>
+      </c>
+      <c r="G58">
+        <v>25.7</v>
+      </c>
+      <c r="H58">
+        <v>148.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>128.4</v>
+      </c>
+      <c r="K58">
+        <v>146.5</v>
+      </c>
+      <c r="L58">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M58">
+        <v>88.32734400000001</v>
+      </c>
+      <c r="N58">
+        <v>-106.427344</v>
+      </c>
+      <c r="O58">
+        <v>-20.22119536</v>
+      </c>
+      <c r="P58">
+        <v>-86.20614864000001</v>
+      </c>
+      <c r="Q58">
+        <v>60.29385135999999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1312810522438416</v>
+      </c>
+      <c r="T58">
+        <v>1.254011122174726</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.03893471539232514</v>
+      </c>
+      <c r="W58">
+        <v>0.2480976100356873</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.2049195546964482</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1986983246072752</v>
+      </c>
+      <c r="C59">
+        <v>-191.6588580911402</v>
+      </c>
+      <c r="D59">
+        <v>159.1261419088598</v>
+      </c>
+      <c r="E59">
+        <v>-135.715</v>
+      </c>
+      <c r="F59">
+        <v>376.485</v>
+      </c>
+      <c r="G59">
+        <v>25.7</v>
+      </c>
+      <c r="H59">
+        <v>148.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>128.4</v>
+      </c>
+      <c r="K59">
+        <v>146.5</v>
+      </c>
+      <c r="L59">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M59">
+        <v>89.90461800000001</v>
+      </c>
+      <c r="N59">
+        <v>-108.004618</v>
+      </c>
+      <c r="O59">
+        <v>-20.52087741999999</v>
+      </c>
+      <c r="P59">
+        <v>-87.48374058000002</v>
+      </c>
+      <c r="Q59">
+        <v>59.01625941999998</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1334317743890472</v>
+      </c>
+      <c r="T59">
+        <v>1.283174171527627</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.03825165021000364</v>
+      </c>
+      <c r="W59">
+        <v>0.2479344940701489</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.2013244747894929</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2006983246072752</v>
+      </c>
+      <c r="C60">
+        <v>-200.229612119724</v>
+      </c>
+      <c r="D60">
+        <v>157.160387880276</v>
+      </c>
+      <c r="E60">
+        <v>-129.1100000000001</v>
+      </c>
+      <c r="F60">
+        <v>383.09</v>
+      </c>
+      <c r="G60">
+        <v>25.7</v>
+      </c>
+      <c r="H60">
+        <v>148.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>128.4</v>
+      </c>
+      <c r="K60">
+        <v>146.5</v>
+      </c>
+      <c r="L60">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M60">
+        <v>91.481892</v>
+      </c>
+      <c r="N60">
+        <v>-109.581892</v>
+      </c>
+      <c r="O60">
+        <v>-20.82055947999999</v>
+      </c>
+      <c r="P60">
+        <v>-88.76133252</v>
+      </c>
+      <c r="Q60">
+        <v>57.73866748</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1356849118745007</v>
+      </c>
+      <c r="T60">
+        <v>1.313725937516379</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.03759213899948635</v>
+      </c>
+      <c r="W60">
+        <v>0.2477770027930774</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.1978533631551913</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2026983246072752</v>
+      </c>
+      <c r="C61">
+        <v>-208.7523911849689</v>
+      </c>
+      <c r="D61">
+        <v>155.2426088150311</v>
+      </c>
+      <c r="E61">
+        <v>-122.5050000000001</v>
+      </c>
+      <c r="F61">
+        <v>389.695</v>
+      </c>
+      <c r="G61">
+        <v>25.7</v>
+      </c>
+      <c r="H61">
+        <v>148.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>128.4</v>
+      </c>
+      <c r="K61">
+        <v>146.5</v>
+      </c>
+      <c r="L61">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M61">
+        <v>93.059166</v>
+      </c>
+      <c r="N61">
+        <v>-111.159166</v>
+      </c>
+      <c r="O61">
+        <v>-21.12024153999999</v>
+      </c>
+      <c r="P61">
+        <v>-90.03892446</v>
+      </c>
+      <c r="Q61">
+        <v>56.46107554</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1380479585055861</v>
+      </c>
+      <c r="T61">
+        <v>1.345768033553364</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.03695498410118996</v>
+      </c>
+      <c r="W61">
+        <v>0.2476248502033642</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.1944999163220524</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2046983246072752</v>
+      </c>
+      <c r="C62">
+        <v>-217.2289303844458</v>
+      </c>
+      <c r="D62">
+        <v>153.3710696155542</v>
+      </c>
+      <c r="E62">
+        <v>-115.9</v>
+      </c>
+      <c r="F62">
+        <v>396.3</v>
+      </c>
+      <c r="G62">
+        <v>25.7</v>
+      </c>
+      <c r="H62">
+        <v>148.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>128.4</v>
+      </c>
+      <c r="K62">
+        <v>146.5</v>
+      </c>
+      <c r="L62">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M62">
+        <v>94.63644000000001</v>
+      </c>
+      <c r="N62">
+        <v>-112.73644</v>
+      </c>
+      <c r="O62">
+        <v>-21.41992359999999</v>
+      </c>
+      <c r="P62">
+        <v>-91.31651640000001</v>
+      </c>
+      <c r="Q62">
+        <v>55.18348359999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1405291574682258</v>
+      </c>
+      <c r="T62">
+        <v>1.379412234392198</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.03633906769950346</v>
+      </c>
+      <c r="W62">
+        <v>0.2474777693666414</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.1912582510500183</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2066983246072752</v>
+      </c>
+      <c r="C63">
+        <v>-225.6608821419967</v>
+      </c>
+      <c r="D63">
+        <v>151.5441178580033</v>
+      </c>
+      <c r="E63">
+        <v>-109.2950000000001</v>
+      </c>
+      <c r="F63">
+        <v>402.905</v>
+      </c>
+      <c r="G63">
+        <v>25.7</v>
+      </c>
+      <c r="H63">
+        <v>148.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>128.4</v>
+      </c>
+      <c r="K63">
+        <v>146.5</v>
+      </c>
+      <c r="L63">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M63">
+        <v>96.213714</v>
+      </c>
+      <c r="N63">
+        <v>-114.313714</v>
+      </c>
+      <c r="O63">
+        <v>-21.71960565999999</v>
+      </c>
+      <c r="P63">
+        <v>-92.59410833999999</v>
+      </c>
+      <c r="Q63">
+        <v>53.90589166000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1431375974033085</v>
+      </c>
+      <c r="T63">
+        <v>1.414781778863793</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.03574334527820013</v>
+      </c>
+      <c r="W63">
+        <v>0.2473355108524342</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.1881228698852639</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2086983246072752</v>
+      </c>
+      <c r="C64">
+        <v>-234.0498210738055</v>
+      </c>
+      <c r="D64">
+        <v>149.7601789261945</v>
+      </c>
+      <c r="E64">
+        <v>-102.6900000000001</v>
+      </c>
+      <c r="F64">
+        <v>409.51</v>
+      </c>
+      <c r="G64">
+        <v>25.7</v>
+      </c>
+      <c r="H64">
+        <v>148.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>128.4</v>
+      </c>
+      <c r="K64">
+        <v>146.5</v>
+      </c>
+      <c r="L64">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M64">
+        <v>97.790988</v>
+      </c>
+      <c r="N64">
+        <v>-115.890988</v>
+      </c>
+      <c r="O64">
+        <v>-22.01928771999999</v>
+      </c>
+      <c r="P64">
+        <v>-93.87170028</v>
+      </c>
+      <c r="Q64">
+        <v>52.62829972</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.145883323650764</v>
+      </c>
+      <c r="T64">
+        <v>1.452012878307577</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.0351668397091969</v>
+      </c>
+      <c r="W64">
+        <v>0.2471978413225562</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.1850886300484049</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2106983246072752</v>
+      </c>
+      <c r="C65">
+        <v>-242.397248514775</v>
+      </c>
+      <c r="D65">
+        <v>148.017751485225</v>
+      </c>
+      <c r="E65">
+        <v>-96.08500000000004</v>
+      </c>
+      <c r="F65">
+        <v>416.115</v>
+      </c>
+      <c r="G65">
+        <v>25.7</v>
+      </c>
+      <c r="H65">
+        <v>148.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>128.4</v>
+      </c>
+      <c r="K65">
+        <v>146.5</v>
+      </c>
+      <c r="L65">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M65">
+        <v>99.368262</v>
+      </c>
+      <c r="N65">
+        <v>-117.468262</v>
+      </c>
+      <c r="O65">
+        <v>-22.31896977999999</v>
+      </c>
+      <c r="P65">
+        <v>-95.14929222000001</v>
+      </c>
+      <c r="Q65">
+        <v>51.35070777999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1487774675332171</v>
+      </c>
+      <c r="T65">
+        <v>1.491256469613187</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.03460863590428902</v>
+      </c>
+      <c r="W65">
+        <v>0.2470645422539442</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.1821507152857318</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2126983246072752</v>
+      </c>
+      <c r="C66">
+        <v>-250.7045967325568</v>
+      </c>
+      <c r="D66">
+        <v>146.3154032674432</v>
+      </c>
+      <c r="E66">
+        <v>-89.48000000000002</v>
+      </c>
+      <c r="F66">
+        <v>422.72</v>
+      </c>
+      <c r="G66">
+        <v>25.7</v>
+      </c>
+      <c r="H66">
+        <v>148.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>128.4</v>
+      </c>
+      <c r="K66">
+        <v>146.5</v>
+      </c>
+      <c r="L66">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M66">
+        <v>100.945536</v>
+      </c>
+      <c r="N66">
+        <v>-119.045536</v>
+      </c>
+      <c r="O66">
+        <v>-22.61865183999999</v>
+      </c>
+      <c r="P66">
+        <v>-96.42688416000001</v>
+      </c>
+      <c r="Q66">
+        <v>50.07311583999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1518323971869175</v>
+      </c>
+      <c r="T66">
+        <v>1.532680260435776</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.0340678759682845</v>
+      </c>
+      <c r="W66">
+        <v>0.2469354087812263</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.179304610359392</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2146983246072752</v>
+      </c>
+      <c r="C67">
+        <v>-258.973232854096</v>
+      </c>
+      <c r="D67">
+        <v>144.651767145904</v>
+      </c>
+      <c r="E67">
+        <v>-82.87500000000006</v>
+      </c>
+      <c r="F67">
+        <v>429.325</v>
+      </c>
+      <c r="G67">
+        <v>25.7</v>
+      </c>
+      <c r="H67">
+        <v>148.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>128.4</v>
+      </c>
+      <c r="K67">
+        <v>146.5</v>
+      </c>
+      <c r="L67">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M67">
+        <v>102.52281</v>
+      </c>
+      <c r="N67">
+        <v>-120.62281</v>
+      </c>
+      <c r="O67">
+        <v>-22.91833389999999</v>
+      </c>
+      <c r="P67">
+        <v>-97.70447610000001</v>
+      </c>
+      <c r="Q67">
+        <v>48.79552389999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1550618942494009</v>
+      </c>
+      <c r="T67">
+        <v>1.576471125019655</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.03354375479954166</v>
+      </c>
+      <c r="W67">
+        <v>0.2468102486461305</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.1765460778923247</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2166983246072752</v>
+      </c>
+      <c r="C68">
+        <v>-267.2044625273122</v>
+      </c>
+      <c r="D68">
+        <v>143.0255374726878</v>
+      </c>
+      <c r="E68">
+        <v>-76.27000000000004</v>
+      </c>
+      <c r="F68">
+        <v>435.93</v>
+      </c>
+      <c r="G68">
+        <v>25.7</v>
+      </c>
+      <c r="H68">
+        <v>148.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>128.4</v>
+      </c>
+      <c r="K68">
+        <v>146.5</v>
+      </c>
+      <c r="L68">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M68">
+        <v>104.100084</v>
+      </c>
+      <c r="N68">
+        <v>-122.200084</v>
+      </c>
+      <c r="O68">
+        <v>-23.21801596</v>
+      </c>
+      <c r="P68">
+        <v>-98.98206804</v>
+      </c>
+      <c r="Q68">
+        <v>47.51793196</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1584813617273244</v>
+      </c>
+      <c r="T68">
+        <v>1.622837922814351</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.0330355160904577</v>
+      </c>
+      <c r="W68">
+        <v>0.2466888812424013</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.1738711373181985</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2186983246072752</v>
+      </c>
+      <c r="C69">
+        <v>-275.3995333385321</v>
+      </c>
+      <c r="D69">
+        <v>141.4354666614679</v>
+      </c>
+      <c r="E69">
+        <v>-69.66500000000002</v>
+      </c>
+      <c r="F69">
+        <v>442.535</v>
+      </c>
+      <c r="G69">
+        <v>25.7</v>
+      </c>
+      <c r="H69">
+        <v>148.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>128.4</v>
+      </c>
+      <c r="K69">
+        <v>146.5</v>
+      </c>
+      <c r="L69">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M69">
+        <v>105.677358</v>
+      </c>
+      <c r="N69">
+        <v>-123.777358</v>
+      </c>
+      <c r="O69">
+        <v>-23.51769801999999</v>
+      </c>
+      <c r="P69">
+        <v>-100.25965998</v>
+      </c>
+      <c r="Q69">
+        <v>46.24034001999999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1621080696584555</v>
+      </c>
+      <c r="T69">
+        <v>1.672014829566301</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.03254244868612251</v>
+      </c>
+      <c r="W69">
+        <v>0.2465711367462461</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.1712760457164342</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2206983246072752</v>
+      </c>
+      <c r="C70">
+        <v>-283.5596380044693</v>
+      </c>
+      <c r="D70">
+        <v>139.8803619955307</v>
+      </c>
+      <c r="E70">
+        <v>-63.06</v>
+      </c>
+      <c r="F70">
+        <v>449.14</v>
+      </c>
+      <c r="G70">
+        <v>25.7</v>
+      </c>
+      <c r="H70">
+        <v>148.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>128.4</v>
+      </c>
+      <c r="K70">
+        <v>146.5</v>
+      </c>
+      <c r="L70">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M70">
+        <v>107.254632</v>
+      </c>
+      <c r="N70">
+        <v>-125.354632</v>
+      </c>
+      <c r="O70">
+        <v>-23.81738008</v>
+      </c>
+      <c r="P70">
+        <v>-101.53725192</v>
+      </c>
+      <c r="Q70">
+        <v>44.96274807999998</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1659614468352822</v>
+      </c>
+      <c r="T70">
+        <v>1.724265292990248</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.03206388326426776</v>
+      </c>
+      <c r="W70">
+        <v>0.2464568553235071</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.1687572803382513</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2226983246072752</v>
+      </c>
+      <c r="C71">
+        <v>-291.685917355918</v>
+      </c>
+      <c r="D71">
+        <v>138.359082644082</v>
+      </c>
+      <c r="E71">
+        <v>-56.45499999999998</v>
+      </c>
+      <c r="F71">
+        <v>455.7450000000001</v>
+      </c>
+      <c r="G71">
+        <v>25.7</v>
+      </c>
+      <c r="H71">
+        <v>148.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>128.4</v>
+      </c>
+      <c r="K71">
+        <v>146.5</v>
+      </c>
+      <c r="L71">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M71">
+        <v>108.831906</v>
+      </c>
+      <c r="N71">
+        <v>-126.931906</v>
+      </c>
+      <c r="O71">
+        <v>-24.11706213999999</v>
+      </c>
+      <c r="P71">
+        <v>-102.81484386</v>
+      </c>
+      <c r="Q71">
+        <v>43.68515613999998</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1700634289912591</v>
+      </c>
+      <c r="T71">
+        <v>1.77988675405445</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.03159918930391605</v>
+      </c>
+      <c r="W71">
+        <v>0.2463458864057751</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.1663115226521898</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2246983246072752</v>
+      </c>
+      <c r="C72">
+        <v>-299.779463128844</v>
+      </c>
+      <c r="D72">
+        <v>136.8705368711561</v>
+      </c>
+      <c r="E72">
+        <v>-49.85000000000002</v>
+      </c>
+      <c r="F72">
+        <v>462.35</v>
+      </c>
+      <c r="G72">
+        <v>25.7</v>
+      </c>
+      <c r="H72">
+        <v>148.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>128.4</v>
+      </c>
+      <c r="K72">
+        <v>146.5</v>
+      </c>
+      <c r="L72">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M72">
+        <v>110.40918</v>
+      </c>
+      <c r="N72">
+        <v>-128.50918</v>
+      </c>
+      <c r="O72">
+        <v>-24.4167442</v>
+      </c>
+      <c r="P72">
+        <v>-104.0924358</v>
+      </c>
+      <c r="Q72">
+        <v>42.40756419999998</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.174438876624301</v>
+      </c>
+      <c r="T72">
+        <v>1.839216312522931</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.03114777231386012</v>
+      </c>
+      <c r="W72">
+        <v>0.2462380880285498</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.1639356437571586</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2266983246072752</v>
+      </c>
+      <c r="C73">
+        <v>-307.8413205772243</v>
+      </c>
+      <c r="D73">
+        <v>135.4136794227757</v>
+      </c>
+      <c r="E73">
+        <v>-43.24500000000006</v>
+      </c>
+      <c r="F73">
+        <v>468.955</v>
+      </c>
+      <c r="G73">
+        <v>25.7</v>
+      </c>
+      <c r="H73">
+        <v>148.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>128.4</v>
+      </c>
+      <c r="K73">
+        <v>146.5</v>
+      </c>
+      <c r="L73">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M73">
+        <v>111.986454</v>
+      </c>
+      <c r="N73">
+        <v>-130.086454</v>
+      </c>
+      <c r="O73">
+        <v>-24.71642626</v>
+      </c>
+      <c r="P73">
+        <v>-105.37002774</v>
+      </c>
+      <c r="Q73">
+        <v>41.12997225999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1791160792665183</v>
+      </c>
+      <c r="T73">
+        <v>1.902637564678894</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.03070907129535504</v>
+      </c>
+      <c r="W73">
+        <v>0.2461333262253308</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.1616266910281845</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2286983246072752</v>
+      </c>
+      <c r="C74">
+        <v>-315.8724909207787</v>
+      </c>
+      <c r="D74">
+        <v>133.9875090792213</v>
+      </c>
+      <c r="E74">
+        <v>-36.64000000000004</v>
+      </c>
+      <c r="F74">
+        <v>475.56</v>
+      </c>
+      <c r="G74">
+        <v>25.7</v>
+      </c>
+      <c r="H74">
+        <v>148.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>128.4</v>
+      </c>
+      <c r="K74">
+        <v>146.5</v>
+      </c>
+      <c r="L74">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M74">
+        <v>113.563728</v>
+      </c>
+      <c r="N74">
+        <v>-131.663728</v>
+      </c>
+      <c r="O74">
+        <v>-25.01610831999999</v>
+      </c>
+      <c r="P74">
+        <v>-106.64761968</v>
+      </c>
+      <c r="Q74">
+        <v>39.85238031999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1841273678117511</v>
+      </c>
+      <c r="T74">
+        <v>1.970588906274569</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.03028255641625288</v>
+      </c>
+      <c r="W74">
+        <v>0.2460314744722012</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.1593818758750152</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2306983246072752</v>
+      </c>
+      <c r="C75">
+        <v>-323.8739336396344</v>
+      </c>
+      <c r="D75">
+        <v>132.5910663603656</v>
+      </c>
+      <c r="E75">
+        <v>-30.03500000000008</v>
+      </c>
+      <c r="F75">
+        <v>482.165</v>
+      </c>
+      <c r="G75">
+        <v>25.7</v>
+      </c>
+      <c r="H75">
+        <v>148.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>128.4</v>
+      </c>
+      <c r="K75">
+        <v>146.5</v>
+      </c>
+      <c r="L75">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M75">
+        <v>115.141002</v>
+      </c>
+      <c r="N75">
+        <v>-133.241002</v>
+      </c>
+      <c r="O75">
+        <v>-25.31579037999999</v>
+      </c>
+      <c r="P75">
+        <v>-107.92521162</v>
+      </c>
+      <c r="Q75">
+        <v>38.57478838</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.18950986291589</v>
+      </c>
+      <c r="T75">
+        <v>2.043573680581034</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.02986772687630422</v>
+      </c>
+      <c r="W75">
+        <v>0.2459324131780614</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.1571985625068641</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2326983246072752</v>
+      </c>
+      <c r="C76">
+        <v>-331.8465686269807</v>
+      </c>
+      <c r="D76">
+        <v>131.2234313730193</v>
+      </c>
+      <c r="E76">
+        <v>-23.43000000000006</v>
+      </c>
+      <c r="F76">
+        <v>488.77</v>
+      </c>
+      <c r="G76">
+        <v>25.7</v>
+      </c>
+      <c r="H76">
+        <v>148.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>128.4</v>
+      </c>
+      <c r="K76">
+        <v>146.5</v>
+      </c>
+      <c r="L76">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M76">
+        <v>116.718276</v>
+      </c>
+      <c r="N76">
+        <v>-134.818276</v>
+      </c>
+      <c r="O76">
+        <v>-25.61547243999999</v>
+      </c>
+      <c r="P76">
+        <v>-109.20280356</v>
+      </c>
+      <c r="Q76">
+        <v>37.29719643999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1953063961049627</v>
+      </c>
+      <c r="T76">
+        <v>2.122172668295689</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.02946410894554335</v>
+      </c>
+      <c r="W76">
+        <v>0.2458360292161958</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.155074257608123</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2346983246072752</v>
+      </c>
+      <c r="C77">
+        <v>-339.7912782098583</v>
+      </c>
+      <c r="D77">
+        <v>129.8837217901417</v>
+      </c>
+      <c r="E77">
+        <v>-16.82500000000005</v>
+      </c>
+      <c r="F77">
+        <v>495.375</v>
+      </c>
+      <c r="G77">
+        <v>25.7</v>
+      </c>
+      <c r="H77">
+        <v>148.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>128.4</v>
+      </c>
+      <c r="K77">
+        <v>146.5</v>
+      </c>
+      <c r="L77">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M77">
+        <v>118.29555</v>
+      </c>
+      <c r="N77">
+        <v>-136.39555</v>
+      </c>
+      <c r="O77">
+        <v>-25.9151545</v>
+      </c>
+      <c r="P77">
+        <v>-110.4803955</v>
+      </c>
+      <c r="Q77">
+        <v>36.01960449999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2015666519491613</v>
+      </c>
+      <c r="T77">
+        <v>2.207059575027517</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.02907125415960277</v>
+      </c>
+      <c r="W77">
+        <v>0.2457422154933132</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.1530066008400148</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2366983246072752</v>
+      </c>
+      <c r="C78">
+        <v>-347.7089090474149</v>
+      </c>
+      <c r="D78">
+        <v>128.5710909525852</v>
+      </c>
+      <c r="E78">
+        <v>-10.22000000000003</v>
+      </c>
+      <c r="F78">
+        <v>501.98</v>
+      </c>
+      <c r="G78">
+        <v>25.7</v>
+      </c>
+      <c r="H78">
+        <v>148.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>128.4</v>
+      </c>
+      <c r="K78">
+        <v>146.5</v>
+      </c>
+      <c r="L78">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M78">
+        <v>119.872824</v>
+      </c>
+      <c r="N78">
+        <v>-137.972824</v>
+      </c>
+      <c r="O78">
+        <v>-26.21483655999999</v>
+      </c>
+      <c r="P78">
+        <v>-111.75798744</v>
+      </c>
+      <c r="Q78">
+        <v>34.74201255999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2083485957803763</v>
+      </c>
+      <c r="T78">
+        <v>2.299020390653664</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.02868873765750274</v>
+      </c>
+      <c r="W78">
+        <v>0.2456508705526116</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.1509933560921197</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2386983246072752</v>
+      </c>
+      <c r="C79">
+        <v>-355.6002739152063</v>
+      </c>
+      <c r="D79">
+        <v>127.2847260847937</v>
+      </c>
+      <c r="E79">
+        <v>-3.615000000000009</v>
+      </c>
+      <c r="F79">
+        <v>508.585</v>
+      </c>
+      <c r="G79">
+        <v>25.7</v>
+      </c>
+      <c r="H79">
+        <v>148.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>128.4</v>
+      </c>
+      <c r="K79">
+        <v>146.5</v>
+      </c>
+      <c r="L79">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M79">
+        <v>121.450098</v>
+      </c>
+      <c r="N79">
+        <v>-139.550098</v>
+      </c>
+      <c r="O79">
+        <v>-26.51451861999999</v>
+      </c>
+      <c r="P79">
+        <v>-113.03557938</v>
+      </c>
+      <c r="Q79">
+        <v>33.46442062</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.215720273857784</v>
+      </c>
+      <c r="T79">
+        <v>2.398977798942954</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.02831615664896374</v>
+      </c>
+      <c r="W79">
+        <v>0.2455618982077726</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.1490324034155985</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2406983246072752</v>
+      </c>
+      <c r="C80">
+        <v>-363.4661533834474</v>
+      </c>
+      <c r="D80">
+        <v>126.0238466165526</v>
+      </c>
+      <c r="E80">
+        <v>2.990000000000009</v>
+      </c>
+      <c r="F80">
+        <v>515.1900000000001</v>
+      </c>
+      <c r="G80">
+        <v>25.7</v>
+      </c>
+      <c r="H80">
+        <v>148.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>128.4</v>
+      </c>
+      <c r="K80">
+        <v>146.5</v>
+      </c>
+      <c r="L80">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M80">
+        <v>123.027372</v>
+      </c>
+      <c r="N80">
+        <v>-141.127372</v>
+      </c>
+      <c r="O80">
+        <v>-26.81420068</v>
+      </c>
+      <c r="P80">
+        <v>-114.31317132</v>
+      </c>
+      <c r="Q80">
+        <v>32.18682867999999</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2237621044876833</v>
+      </c>
+      <c r="T80">
+        <v>2.508022244349452</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.02795312899961805</v>
+      </c>
+      <c r="W80">
+        <v>0.2454752072051088</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.1471217315769371</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2426983246072752</v>
+      </c>
+      <c r="C81">
+        <v>-371.307297396492</v>
+      </c>
+      <c r="D81">
+        <v>124.7877026035081</v>
+      </c>
+      <c r="E81">
+        <v>9.595000000000027</v>
+      </c>
+      <c r="F81">
+        <v>521.7950000000001</v>
+      </c>
+      <c r="G81">
+        <v>25.7</v>
+      </c>
+      <c r="H81">
+        <v>148.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>128.4</v>
+      </c>
+      <c r="K81">
+        <v>146.5</v>
+      </c>
+      <c r="L81">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M81">
+        <v>124.604646</v>
+      </c>
+      <c r="N81">
+        <v>-142.704646</v>
+      </c>
+      <c r="O81">
+        <v>-27.11388274</v>
+      </c>
+      <c r="P81">
+        <v>-115.59076326</v>
+      </c>
+      <c r="Q81">
+        <v>30.90923673999997</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2325698237490015</v>
+      </c>
+      <c r="T81">
+        <v>2.627451875032759</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.02759929192367351</v>
+      </c>
+      <c r="W81">
+        <v>0.2453907109113733</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.1452594311772293</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2446983246072752</v>
+      </c>
+      <c r="C82">
+        <v>-379.1244267602594</v>
+      </c>
+      <c r="D82">
+        <v>123.5755732397405</v>
+      </c>
+      <c r="E82">
+        <v>16.19999999999993</v>
+      </c>
+      <c r="F82">
+        <v>528.4</v>
+      </c>
+      <c r="G82">
+        <v>25.7</v>
+      </c>
+      <c r="H82">
+        <v>148.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>128.4</v>
+      </c>
+      <c r="K82">
+        <v>146.5</v>
+      </c>
+      <c r="L82">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M82">
+        <v>126.18192</v>
+      </c>
+      <c r="N82">
+        <v>-144.28192</v>
+      </c>
+      <c r="O82">
+        <v>-27.4135648</v>
+      </c>
+      <c r="P82">
+        <v>-116.8683552</v>
+      </c>
+      <c r="Q82">
+        <v>29.63164479999998</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2422583149364516</v>
+      </c>
+      <c r="T82">
+        <v>2.758824468784397</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.0272543007746276</v>
+      </c>
+      <c r="W82">
+        <v>0.2453083270249811</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.1434436882875139</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2466983246072752</v>
+      </c>
+      <c r="C83">
+        <v>-386.9182345438063</v>
+      </c>
+      <c r="D83">
+        <v>122.3867654561937</v>
+      </c>
+      <c r="E83">
+        <v>22.80499999999995</v>
+      </c>
+      <c r="F83">
+        <v>535.005</v>
+      </c>
+      <c r="G83">
+        <v>25.7</v>
+      </c>
+      <c r="H83">
+        <v>148.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>128.4</v>
+      </c>
+      <c r="K83">
+        <v>146.5</v>
+      </c>
+      <c r="L83">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M83">
+        <v>127.759194</v>
+      </c>
+      <c r="N83">
+        <v>-145.859194</v>
+      </c>
+      <c r="O83">
+        <v>-27.71324685999999</v>
+      </c>
+      <c r="P83">
+        <v>-118.14594714</v>
+      </c>
+      <c r="Q83">
+        <v>28.35405286</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2529666473015281</v>
+      </c>
+      <c r="T83">
+        <v>2.904025756615155</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.02691782792555813</v>
+      </c>
+      <c r="W83">
+        <v>0.2452279773086233</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.1416727785555691</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2486983246072752</v>
+      </c>
+      <c r="C84">
+        <v>-394.6893874007687</v>
+      </c>
+      <c r="D84">
+        <v>121.2206125992313</v>
+      </c>
+      <c r="E84">
+        <v>29.40999999999997</v>
+      </c>
+      <c r="F84">
+        <v>541.61</v>
+      </c>
+      <c r="G84">
+        <v>25.7</v>
+      </c>
+      <c r="H84">
+        <v>148.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>128.4</v>
+      </c>
+      <c r="K84">
+        <v>146.5</v>
+      </c>
+      <c r="L84">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M84">
+        <v>129.336468</v>
+      </c>
+      <c r="N84">
+        <v>-147.436468</v>
+      </c>
+      <c r="O84">
+        <v>-28.01292891999999</v>
+      </c>
+      <c r="P84">
+        <v>-119.42353908</v>
+      </c>
+      <c r="Q84">
+        <v>27.07646092</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2648647943738351</v>
+      </c>
+      <c r="T84">
+        <v>3.065360520871553</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.026589561731344</v>
+      </c>
+      <c r="W84">
+        <v>0.245149587341445</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.1399450617439157</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2506983246072752</v>
+      </c>
+      <c r="C85">
+        <v>-402.4385268159708</v>
+      </c>
+      <c r="D85">
+        <v>120.0764731840293</v>
+      </c>
+      <c r="E85">
+        <v>36.01499999999999</v>
+      </c>
+      <c r="F85">
+        <v>548.215</v>
+      </c>
+      <c r="G85">
+        <v>25.7</v>
+      </c>
+      <c r="H85">
+        <v>148.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>128.4</v>
+      </c>
+      <c r="K85">
+        <v>146.5</v>
+      </c>
+      <c r="L85">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M85">
+        <v>130.913742</v>
+      </c>
+      <c r="N85">
+        <v>-149.013742</v>
+      </c>
+      <c r="O85">
+        <v>-28.31261098</v>
+      </c>
+      <c r="P85">
+        <v>-120.70113102</v>
+      </c>
+      <c r="Q85">
+        <v>25.79886897999998</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.278162723454649</v>
+      </c>
+      <c r="T85">
+        <v>3.245675845628703</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.02626920556590612</v>
+      </c>
+      <c r="W85">
+        <v>0.2450730862891384</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.1382589766626638</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2526983246072752</v>
+      </c>
+      <c r="C86">
+        <v>-410.1662702820964</v>
+      </c>
+      <c r="D86">
+        <v>118.9537297179035</v>
+      </c>
+      <c r="E86">
+        <v>42.61999999999989</v>
+      </c>
+      <c r="F86">
+        <v>554.8199999999999</v>
+      </c>
+      <c r="G86">
+        <v>25.7</v>
+      </c>
+      <c r="H86">
+        <v>148.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>128.4</v>
+      </c>
+      <c r="K86">
+        <v>146.5</v>
+      </c>
+      <c r="L86">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M86">
+        <v>132.491016</v>
+      </c>
+      <c r="N86">
+        <v>-150.591016</v>
+      </c>
+      <c r="O86">
+        <v>-28.61229303999999</v>
+      </c>
+      <c r="P86">
+        <v>-121.97872296</v>
+      </c>
+      <c r="Q86">
+        <v>24.52127704</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2931228936705644</v>
+      </c>
+      <c r="T86">
+        <v>3.448530585980495</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.02595647692821676</v>
+      </c>
+      <c r="W86">
+        <v>0.2449984066904582</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.1366130364642988</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2546983246072752</v>
+      </c>
+      <c r="C87">
+        <v>-417.87321241096</v>
+      </c>
+      <c r="D87">
+        <v>117.85178758904</v>
+      </c>
+      <c r="E87">
+        <v>49.22499999999991</v>
+      </c>
+      <c r="F87">
+        <v>561.425</v>
+      </c>
+      <c r="G87">
+        <v>25.7</v>
+      </c>
+      <c r="H87">
+        <v>148.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>128.4</v>
+      </c>
+      <c r="K87">
+        <v>146.5</v>
+      </c>
+      <c r="L87">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M87">
+        <v>134.06829</v>
+      </c>
+      <c r="N87">
+        <v>-152.16829</v>
+      </c>
+      <c r="O87">
+        <v>-28.91197509999999</v>
+      </c>
+      <c r="P87">
+        <v>-123.2563149</v>
+      </c>
+      <c r="Q87">
+        <v>23.24368510000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.310077753248602</v>
+      </c>
+      <c r="T87">
+        <v>3.678432625045862</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.02565110661141422</v>
+      </c>
+      <c r="W87">
+        <v>0.2449254842588057</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.1350058242706011</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2566983246072752</v>
+      </c>
+      <c r="C88">
+        <v>-425.5599259835765</v>
+      </c>
+      <c r="D88">
+        <v>116.7700740164235</v>
+      </c>
+      <c r="E88">
+        <v>55.82999999999993</v>
+      </c>
+      <c r="F88">
+        <v>568.03</v>
+      </c>
+      <c r="G88">
+        <v>25.7</v>
+      </c>
+      <c r="H88">
+        <v>148.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>128.4</v>
+      </c>
+      <c r="K88">
+        <v>146.5</v>
+      </c>
+      <c r="L88">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M88">
+        <v>135.645564</v>
+      </c>
+      <c r="N88">
+        <v>-153.745564</v>
+      </c>
+      <c r="O88">
+        <v>-29.21165715999999</v>
+      </c>
+      <c r="P88">
+        <v>-124.53390684</v>
+      </c>
+      <c r="Q88">
+        <v>21.96609315999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3294547356235022</v>
+      </c>
+      <c r="T88">
+        <v>3.941177812549137</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.02535283792988614</v>
+      </c>
+      <c r="W88">
+        <v>0.2448542576976568</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.1334359891046639</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2586983246072752</v>
+      </c>
+      <c r="C89">
+        <v>-433.22696294293</v>
+      </c>
+      <c r="D89">
+        <v>115.70803705707</v>
+      </c>
+      <c r="E89">
+        <v>62.43499999999995</v>
+      </c>
+      <c r="F89">
+        <v>574.635</v>
+      </c>
+      <c r="G89">
+        <v>25.7</v>
+      </c>
+      <c r="H89">
+        <v>148.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>128.4</v>
+      </c>
+      <c r="K89">
+        <v>146.5</v>
+      </c>
+      <c r="L89">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M89">
+        <v>137.222838</v>
+      </c>
+      <c r="N89">
+        <v>-155.322838</v>
+      </c>
+      <c r="O89">
+        <v>-29.51133921999999</v>
+      </c>
+      <c r="P89">
+        <v>-125.81149878</v>
+      </c>
+      <c r="Q89">
+        <v>20.68850122000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3518127922099255</v>
+      </c>
+      <c r="T89">
+        <v>4.244345336591379</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.02506142599965757</v>
+      </c>
+      <c r="W89">
+        <v>0.2447846685287182</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.1319022421034608</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2606983246072752</v>
+      </c>
+      <c r="C90">
+        <v>-440.8748553330538</v>
+      </c>
+      <c r="D90">
+        <v>114.6651446669462</v>
+      </c>
+      <c r="E90">
+        <v>69.03999999999996</v>
+      </c>
+      <c r="F90">
+        <v>581.24</v>
+      </c>
+      <c r="G90">
+        <v>25.7</v>
+      </c>
+      <c r="H90">
+        <v>148.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>128.4</v>
+      </c>
+      <c r="K90">
+        <v>146.5</v>
+      </c>
+      <c r="L90">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M90">
+        <v>138.800112</v>
+      </c>
+      <c r="N90">
+        <v>-156.900112</v>
+      </c>
+      <c r="O90">
+        <v>-29.81102127999999</v>
+      </c>
+      <c r="P90">
+        <v>-127.08909072</v>
+      </c>
+      <c r="Q90">
+        <v>19.41090927999998</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3778971915607526</v>
+      </c>
+      <c r="T90">
+        <v>4.598040781307328</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.02477663706784327</v>
+      </c>
+      <c r="W90">
+        <v>0.244716660931801</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.1304033529886488</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2626983246072752</v>
+      </c>
+      <c r="C91">
+        <v>-448.5041161877795</v>
+      </c>
+      <c r="D91">
+        <v>113.6408838122206</v>
+      </c>
+      <c r="E91">
+        <v>75.64499999999998</v>
+      </c>
+      <c r="F91">
+        <v>587.845</v>
+      </c>
+      <c r="G91">
+        <v>25.7</v>
+      </c>
+      <c r="H91">
+        <v>148.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>128.4</v>
+      </c>
+      <c r="K91">
+        <v>146.5</v>
+      </c>
+      <c r="L91">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M91">
+        <v>140.377386</v>
+      </c>
+      <c r="N91">
+        <v>-158.477386</v>
+      </c>
+      <c r="O91">
+        <v>-30.11070333999999</v>
+      </c>
+      <c r="P91">
+        <v>-128.36668266</v>
+      </c>
+      <c r="Q91">
+        <v>18.13331733999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4087242089753665</v>
+      </c>
+      <c r="T91">
+        <v>5.016044488698904</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.02449824788730571</v>
+      </c>
+      <c r="W91">
+        <v>0.2446501815954886</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.1289381467752932</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2646983246072752</v>
+      </c>
+      <c r="C92">
+        <v>-456.1152403722751</v>
+      </c>
+      <c r="D92">
+        <v>112.6347596277249</v>
+      </c>
+      <c r="E92">
+        <v>82.25</v>
+      </c>
+      <c r="F92">
+        <v>594.45</v>
+      </c>
+      <c r="G92">
+        <v>25.7</v>
+      </c>
+      <c r="H92">
+        <v>148.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>128.4</v>
+      </c>
+      <c r="K92">
+        <v>146.5</v>
+      </c>
+      <c r="L92">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M92">
+        <v>141.95466</v>
+      </c>
+      <c r="N92">
+        <v>-160.05466</v>
+      </c>
+      <c r="O92">
+        <v>-30.4103854</v>
+      </c>
+      <c r="P92">
+        <v>-129.6442746</v>
+      </c>
+      <c r="Q92">
+        <v>16.85572539999998</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4457166298729032</v>
+      </c>
+      <c r="T92">
+        <v>5.517648937568794</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.02422604513300231</v>
+      </c>
+      <c r="W92">
+        <v>0.244585179577761</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.1275055007000121</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2666983246072752</v>
+      </c>
+      <c r="C93">
+        <v>-463.7087053802722</v>
+      </c>
+      <c r="D93">
+        <v>111.6462946197278</v>
+      </c>
+      <c r="E93">
+        <v>88.85500000000002</v>
+      </c>
+      <c r="F93">
+        <v>601.0550000000001</v>
+      </c>
+      <c r="G93">
+        <v>25.7</v>
+      </c>
+      <c r="H93">
+        <v>148.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>128.4</v>
+      </c>
+      <c r="K93">
+        <v>146.5</v>
+      </c>
+      <c r="L93">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M93">
+        <v>143.531934</v>
+      </c>
+      <c r="N93">
+        <v>-161.631934</v>
+      </c>
+      <c r="O93">
+        <v>-30.71006746</v>
+      </c>
+      <c r="P93">
+        <v>-130.92186654</v>
+      </c>
+      <c r="Q93">
+        <v>15.57813345999998</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4909295887476702</v>
+      </c>
+      <c r="T93">
+        <v>6.130721041743104</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.02395982485681546</v>
+      </c>
+      <c r="W93">
+        <v>0.2445216061758075</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.1261043413516605</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2686983246072752</v>
+      </c>
+      <c r="C94">
+        <v>-471.2849720896792</v>
+      </c>
+      <c r="D94">
+        <v>110.6750279103209</v>
+      </c>
+      <c r="E94">
+        <v>95.46000000000004</v>
+      </c>
+      <c r="F94">
+        <v>607.6600000000001</v>
+      </c>
+      <c r="G94">
+        <v>25.7</v>
+      </c>
+      <c r="H94">
+        <v>148.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>128.4</v>
+      </c>
+      <c r="K94">
+        <v>146.5</v>
+      </c>
+      <c r="L94">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M94">
+        <v>145.109208</v>
+      </c>
+      <c r="N94">
+        <v>-163.209208</v>
+      </c>
+      <c r="O94">
+        <v>-31.00974952</v>
+      </c>
+      <c r="P94">
+        <v>-132.19945848</v>
+      </c>
+      <c r="Q94">
+        <v>14.30054151999997</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5474457873411291</v>
+      </c>
+      <c r="T94">
+        <v>6.897061171960996</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.02369939197793704</v>
+      </c>
+      <c r="W94">
+        <v>0.2444594148043314</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.1247336419891423</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2706983246072752</v>
+      </c>
+      <c r="C95">
+        <v>-478.8444854790945</v>
+      </c>
+      <c r="D95">
+        <v>109.7205145209055</v>
+      </c>
+      <c r="E95">
+        <v>102.0649999999999</v>
+      </c>
+      <c r="F95">
+        <v>614.265</v>
+      </c>
+      <c r="G95">
+        <v>25.7</v>
+      </c>
+      <c r="H95">
+        <v>148.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>128.4</v>
+      </c>
+      <c r="K95">
+        <v>146.5</v>
+      </c>
+      <c r="L95">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M95">
+        <v>146.686482</v>
+      </c>
+      <c r="N95">
+        <v>-164.786482</v>
+      </c>
+      <c r="O95">
+        <v>-31.30943157999999</v>
+      </c>
+      <c r="P95">
+        <v>-133.47705042</v>
+      </c>
+      <c r="Q95">
+        <v>13.02294957999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6201094712470048</v>
+      </c>
+      <c r="T95">
+        <v>7.882355625098281</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.02344455980613127</v>
+      </c>
+      <c r="W95">
+        <v>0.2443985608817041</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.1233924200322698</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2726983246072752</v>
+      </c>
+      <c r="C96">
+        <v>-486.3876753075606</v>
+      </c>
+      <c r="D96">
+        <v>108.7823246924394</v>
+      </c>
+      <c r="E96">
+        <v>108.67</v>
+      </c>
+      <c r="F96">
+        <v>620.87</v>
+      </c>
+      <c r="G96">
+        <v>25.7</v>
+      </c>
+      <c r="H96">
+        <v>148.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>128.4</v>
+      </c>
+      <c r="K96">
+        <v>146.5</v>
+      </c>
+      <c r="L96">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M96">
+        <v>148.263756</v>
+      </c>
+      <c r="N96">
+        <v>-166.363756</v>
+      </c>
+      <c r="O96">
+        <v>-31.60911363999999</v>
+      </c>
+      <c r="P96">
+        <v>-134.75464236</v>
+      </c>
+      <c r="Q96">
+        <v>11.74535764000001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7169943831215058</v>
+      </c>
+      <c r="T96">
+        <v>9.196081562614664</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.02319514959542774</v>
+      </c>
+      <c r="W96">
+        <v>0.2443390017233882</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.1220797347127776</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2746983246072752</v>
+      </c>
+      <c r="C97">
+        <v>-493.9149567597374</v>
+      </c>
+      <c r="D97">
+        <v>107.8600432402626</v>
+      </c>
+      <c r="E97">
+        <v>115.275</v>
+      </c>
+      <c r="F97">
+        <v>627.475</v>
+      </c>
+      <c r="G97">
+        <v>25.7</v>
+      </c>
+      <c r="H97">
+        <v>148.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>128.4</v>
+      </c>
+      <c r="K97">
+        <v>146.5</v>
+      </c>
+      <c r="L97">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M97">
+        <v>149.84103</v>
+      </c>
+      <c r="N97">
+        <v>-167.94103</v>
+      </c>
+      <c r="O97">
+        <v>-31.90879569999999</v>
+      </c>
+      <c r="P97">
+        <v>-136.0322343</v>
+      </c>
+      <c r="Q97">
+        <v>10.46776569999997</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8526332597458073</v>
+      </c>
+      <c r="T97">
+        <v>11.0352978751376</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.02295099012600219</v>
+      </c>
+      <c r="W97">
+        <v>0.2442806964420893</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.1207946848736958</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2766983246072752</v>
+      </c>
+      <c r="C98">
+        <v>-501.4267310585334</v>
+      </c>
+      <c r="D98">
+        <v>106.9532689414665</v>
+      </c>
+      <c r="E98">
+        <v>121.8799999999999</v>
+      </c>
+      <c r="F98">
+        <v>634.0799999999999</v>
+      </c>
+      <c r="G98">
+        <v>25.7</v>
+      </c>
+      <c r="H98">
+        <v>148.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>128.4</v>
+      </c>
+      <c r="K98">
+        <v>146.5</v>
+      </c>
+      <c r="L98">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M98">
+        <v>151.418304</v>
+      </c>
+      <c r="N98">
+        <v>-169.518304</v>
+      </c>
+      <c r="O98">
+        <v>-32.20847775999999</v>
+      </c>
+      <c r="P98">
+        <v>-137.30982624</v>
+      </c>
+      <c r="Q98">
+        <v>9.190173760000022</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.056091574682257</v>
+      </c>
+      <c r="T98">
+        <v>13.79412234392197</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.02271191731218967</v>
+      </c>
+      <c r="W98">
+        <v>0.2442236058541509</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.1195364069062614</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2786983246072752</v>
+      </c>
+      <c r="C99">
+        <v>-508.9233860470921</v>
+      </c>
+      <c r="D99">
+        <v>106.0616139529078</v>
+      </c>
+      <c r="E99">
+        <v>128.4849999999999</v>
+      </c>
+      <c r="F99">
+        <v>640.6849999999999</v>
+      </c>
+      <c r="G99">
+        <v>25.7</v>
+      </c>
+      <c r="H99">
+        <v>148.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>128.4</v>
+      </c>
+      <c r="K99">
+        <v>146.5</v>
+      </c>
+      <c r="L99">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M99">
+        <v>152.995578</v>
+      </c>
+      <c r="N99">
+        <v>-171.095578</v>
+      </c>
+      <c r="O99">
+        <v>-32.50815981999999</v>
+      </c>
+      <c r="P99">
+        <v>-138.58741818</v>
+      </c>
+      <c r="Q99">
+        <v>7.912581820000014</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.395188766243009</v>
+      </c>
+      <c r="T99">
+        <v>18.3921631252293</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.02247777383474441</v>
+      </c>
+      <c r="W99">
+        <v>0.244167692391737</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.1183040728144442</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2806983246072752</v>
+      </c>
+      <c r="C100">
+        <v>-516.4052967419066</v>
+      </c>
+      <c r="D100">
+        <v>105.1847032580934</v>
+      </c>
+      <c r="E100">
+        <v>135.0899999999999</v>
+      </c>
+      <c r="F100">
+        <v>647.29</v>
+      </c>
+      <c r="G100">
+        <v>25.7</v>
+      </c>
+      <c r="H100">
+        <v>148.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>128.4</v>
+      </c>
+      <c r="K100">
+        <v>146.5</v>
+      </c>
+      <c r="L100">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M100">
+        <v>154.572852</v>
+      </c>
+      <c r="N100">
+        <v>-172.672852</v>
+      </c>
+      <c r="O100">
+        <v>-32.80784187999999</v>
+      </c>
+      <c r="P100">
+        <v>-139.86501012</v>
+      </c>
+      <c r="Q100">
+        <v>6.634989879999978</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.073383149364514</v>
+      </c>
+      <c r="T100">
+        <v>27.58824468784394</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.02224840879561436</v>
+      </c>
+      <c r="W100">
+        <v>0.2441129200203927</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.1170968883979704</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2826983246072752</v>
+      </c>
+      <c r="C101">
+        <v>-523.8728258587216</v>
+      </c>
+      <c r="D101">
+        <v>104.3221741412784</v>
+      </c>
+      <c r="E101">
+        <v>141.6949999999999</v>
+      </c>
+      <c r="F101">
+        <v>653.895</v>
+      </c>
+      <c r="G101">
+        <v>25.7</v>
+      </c>
+      <c r="H101">
+        <v>148.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>128.4</v>
+      </c>
+      <c r="K101">
+        <v>146.5</v>
+      </c>
+      <c r="L101">
+        <v>-18.09999999999999</v>
+      </c>
+      <c r="M101">
+        <v>156.150126</v>
+      </c>
+      <c r="N101">
+        <v>-174.250126</v>
+      </c>
+      <c r="O101">
+        <v>-33.10752393999999</v>
+      </c>
+      <c r="P101">
+        <v>-141.14260206</v>
+      </c>
+      <c r="Q101">
+        <v>5.357397939999998</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.107966298729028</v>
+      </c>
+      <c r="T101">
+        <v>55.17648937568788</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.02202367739363846</v>
+      </c>
+      <c r="W101">
+        <v>0.2440592541616009</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.1159140915454657</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
